--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -49,18 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,12 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,8 +772,8 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="11" t="n">
-        <v>25.1</v>
+      <c r="D4" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>13.6</v>
@@ -794,7 +782,7 @@
         <v>19.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>13.1</v>
@@ -806,10 +794,10 @@
         <v>4.7</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.2</v>
+        <v>28.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n">
@@ -818,35 +806,39 @@
       <c r="O4" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n">
-        <v>25</v>
+      <c r="P4" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>18</v>
+        <v>1.6</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>5.5</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -860,8 +852,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="11" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>508.2</v>
+      </c>
+      <c r="D5" s="10" t="n"/>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
       </c>
@@ -869,34 +863,34 @@
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>15.7</v>
+        <v>1.7</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M5" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.9</v>
+        <v>6.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1092</v>
+        <v>92.8</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
@@ -905,10 +899,10 @@
         <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>10.4</v>
@@ -920,11 +914,13 @@
         <v>16.8</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y5" s="3" t="n"/>
+        <v>18.3</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>27</v>
+      </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,61 +936,59 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>24.1</v>
+        <v>52.9</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>24.41</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>20.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>43.8</v>
+        <v>41.8</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N6" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>192.8</v>
-      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>145.8</v>
+        <v>43.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17.9</v>
+        <v>13.5</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>18.7</v>
@@ -1003,13 +997,13 @@
         <v>16.6</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>82.5</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1025,76 +1019,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
-      </c>
-      <c r="D7" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.4</v>
+        <v>23.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>16.2</v>
+      <c r="N7" s="8" t="n">
+        <v>83.7</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>17.6</v>
+        <v>718.1</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>77.59999999999999</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>1.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.8</v>
+        <v>20.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1110,61 +1104,59 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17.7</v>
+        <v>12.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>195.9</v>
-      </c>
+        <v>14.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>120.5</v>
+        <v>11.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
@@ -1172,14 +1164,14 @@
       <c r="W8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X8" s="8" t="n">
-        <v>17.8</v>
+      <c r="X8" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>80.8</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1195,72 +1187,78 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>615.6</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G9" s="3" t="n"/>
+        <v>445</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>1183.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>9.1</v>
+      </c>
       <c r="H9" s="3" t="n">
-        <v>63.4</v>
+        <v>63.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>10.8</v>
+        <v>206.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>264.4</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>51.1</v>
+        <v>16.4</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17179190
+1
+</t>
+        </is>
       </c>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>45.9</v>
+        <v>18.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>114</v>
+        <v>173.8</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>26.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>13.6</v>
+        <v>7.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>5301</v>
+        <v>3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>194</v>
+        <v>40.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>16</v>
+        <v>82.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>17.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>90</v>
+        <v>45.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2</v>
+        <v>19.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1276,30 +1274,32 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>445</v>
+        <v>194.8</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>1.8</v>
+      <c r="F10" s="11" t="n">
+        <v>1.6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>14.7</v>
       </c>
@@ -1307,28 +1307,28 @@
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>15.8</v>
+        <v>0.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>21.8</v>
+        <v>880.1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.5</v>
+        <v>62.8</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>18.8</v>
@@ -1337,13 +1337,13 @@
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>89.7</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1088.4</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>154.8</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>22.5</v>
+        <v>298.9</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>13.7</v>
@@ -1371,64 +1371,68 @@
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>33.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>148.1</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>10.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>14.8</v>
+        <v>28.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>468.6</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>19</v>
+        <v>12.5</v>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+198
+</t>
+        </is>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>63.8</v>
+        <v>3.4</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1444,61 +1448,61 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229.5</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>22.4</v>
+        <v>298.9</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13.3</v>
+        <v>18.5</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G12" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>13.9</v>
+        <v>14.8</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>18</v>
+        <v>10.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92</v>
+        <v>94.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R12" s="8" t="n">
-        <v>17.1</v>
+        <v>20.3</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>74.5</v>
+        <v>4.5</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>16.2</v>
+        <v>6.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>16.5</v>
@@ -1507,13 +1511,13 @@
         <v>14.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>17.8</v>
+        <v>1.5</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>40.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1529,10 +1533,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>29322</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>23.6</v>
+        <v>32.4</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>63.6</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>13.8</v>
@@ -1541,16 +1545,16 @@
         <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>19.8</v>
+        <v>49.8</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n">
@@ -1560,43 +1564,41 @@
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>946.4</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>15.8</v>
+        <v>1.1</v>
+      </c>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>58.2</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>16.8</v>
+      <c r="S13" s="8" t="n">
+        <v>68.5</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>15.9</v>
+        <v>1.4</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>85</v>
+        <v>92.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1611,58 +1613,60 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>324</v>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>13.4</v>
+      <c r="E14" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="3" t="n">
+        <v>5.3</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="8" t="n">
-        <v>11</v>
+      <c r="N14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>21.5</v>
+        <v>41.3</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>171.9</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>71.2</v>
+        <v>28.8</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>18.2</v>
@@ -1671,13 +1675,13 @@
         <v>16.6</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>92</v>
+        <v>8.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1693,44 +1697,42 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>307.9</v>
+        <v>1475.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F15" s="13" t="n"/>
+        <v>24.8</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H15" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>15.4</v>
+      <c r="I15" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M15" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>96.8</v>
-      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
@@ -1738,11 +1740,11 @@
       <c r="R15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>6.2</v>
@@ -1754,13 +1756,13 @@
         <v>15.7</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18</v>
+        <v>1.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>885.5</v>
+        <v>341</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1776,72 +1778,78 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1425.9</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F16" s="10" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1107.4</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>644.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O16" s="3" t="n"/>
+      <c r="M16" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="P16" s="3" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>6.3</v>
+        <v>23.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>32.4</v>
+        <v>3994.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>14.8</v>
+        <v>44.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>184.5</v>
+        <v>84.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>28.6</v>
+        <v>25.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>17.5</v>
+        <v>56.1</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>92</v>
+        <v>48.2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1857,47 +1865,47 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>18.8</v>
+        <v>25</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>48.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>16.7</v>
@@ -1906,25 +1914,25 @@
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>16.9</v>
+        <v>0.5</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>15.7</v>
+        <v>1.8</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>86.7</v>
+        <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>50.2</v>
+        <v>9.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1940,49 +1948,53 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>24.9</v>
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F18" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+        <v>10.9</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>14.8</v>
+        <v>18.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="n">
-        <v>3.5</v>
+        <v>21.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>1</v>
+        <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>6.1</v>
@@ -1993,17 +2005,17 @@
       <c r="V18" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>16</v>
+      <c r="W18" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>17.2</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>410.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2019,46 +2031,48 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>428.5</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>440.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>25</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>19.5</v>
+      <c r="F19" s="9" t="n">
+        <v>95.2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>18.7</v>
+        <v>5.4</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>92</v>
-      </c>
+      <c r="M19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="n">
-        <v>51.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2067,28 +2081,28 @@
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>14.4</v>
+        <v>8</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>67.2</v>
+        <v>1.8</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>17</v>
+        <v>18.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>8.1</v>
+        <v>810.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>40.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2104,72 +2118,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>440.6</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E20" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>17.5</v>
+      <c r="F20" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>1.1</v>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="n">
-        <v>10.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>76.8</v>
+        <v>46.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2185,29 +2201,31 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>21.9</v>
+        <v>2461.7</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>41.9</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>18.8</v>
+        <v>14.7</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I21" s="3" t="n"/>
+        <v>14.1</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="J21" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10.9</v>
+        <v>3</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.2</v>
@@ -2215,15 +2233,17 @@
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="O21" s="3" t="n"/>
+      <c r="N21" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="P21" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>21.5</v>
+        <v>7.8</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>41.4</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
@@ -2232,25 +2252,25 @@
         <v>18.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>74.8</v>
+        <v>4</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>1.8</v>
+        <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>1.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>92</v>
+        <v>4.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2266,74 +2286,70 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>261.7</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F22" s="11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>12.5</v>
+        <v>33.2</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="P22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="Q22" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="S22" s="8" t="n">
-        <v>17.8</v>
+      <c r="S22" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.2</v>
+        <v>56.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>45.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2349,43 +2365,41 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>123.3</v>
+        <v>147.7</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="10" t="n">
-        <v>91.8</v>
+      <c r="E23" s="11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>9.4</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>617</v>
-      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>3321.1</v>
-      </c>
+        <v>7.3</v>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>17</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>109</v>
+        <v>179.8</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>88.8</v>
@@ -2394,25 +2408,25 @@
         <v>90.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>414.1</v>
+        <v>41.9</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>94.2</v>
+        <v>44.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>16.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>499.5</v>
+        <v>0.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>10.9</v>
+        <v>158.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2428,58 +2442,54 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1477.9</v>
+        <v>1.4</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>13.9</v>
+      <c r="E24" s="11" t="n">
+        <v>1.9</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="n">
-        <v>21.8</v>
+        <v>1.8</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>18.1</v>
+      <c r="S24" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>8.1</v>
@@ -2488,16 +2498,16 @@
         <v>18.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>158.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2513,51 +2523,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>18.1</v>
+        <v>22.6</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>46.1</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1</v>
+        <v>14.6</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>5.1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M25" s="8" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>1.8</v>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>145.4</v>
       </c>
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>6.6</v>
@@ -2569,16 +2577,16 @@
         <v>16.6</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>94</v>
+        <v>88.5</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2594,22 +2602,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>890.4</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>22.5</v>
+        <v>28.8</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>18.9</v>
+      <c r="F26" s="9" t="n">
+        <v>89.09999999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.3</v>
+        <v>13.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2617,53 +2625,57 @@
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+1198
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>1.4</v>
+        <v>40.6</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>1713</v>
+        <v>3</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>17.9</v>
+        <v>12.5</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>88.5</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2679,10 +2691,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>326</v>
+        <v>53.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>23.5</v>
+        <v>13.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>14.4</v>
@@ -2691,7 +2703,7 @@
         <v>18.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>14.9</v>
@@ -2701,35 +2713,37 @@
         <v>2.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.1</v>
+        <v>15.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
+        <v>16.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>17.9</v>
+        <v>1.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.8</v>
@@ -2738,13 +2752,13 @@
         <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>18.5</v>
+        <v>15.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91</v>
+        <v>83.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2760,58 +2774,62 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>281.8</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>17.9</v>
+        <v>289.8</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.9</v>
+        <v>8.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>15.4</v>
+        <v>7.1</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9799791979277
+2 8
+</t>
+        </is>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="P28" s="3" t="n">
-        <v>0.8</v>
+      <c r="P28" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>76.8</v>
+      <c r="S28" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>6.6</v>
@@ -2822,14 +2840,14 @@
       <c r="W28" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>15.8</v>
+      <c r="X28" s="8" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>830.8</v>
+        <v>85</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2845,16 +2863,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2305.9</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>12.19</v>
+        <v>199.9</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>17.9</v>
+      <c r="F29" s="9" t="n">
+        <v>1.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.1</v>
@@ -2863,41 +2881,41 @@
         <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>714.4</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P29" s="3" t="n"/>
       <c r="Q29" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>19.8</v>
+        <v>17.8</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>82.09999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>18.8</v>
@@ -2905,11 +2923,9 @@
       <c r="W29" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="n">
-        <v>85</v>
+        <v>147.4</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>3.2</v>
@@ -2927,63 +2943,90 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>289.8</v>
-      </c>
-      <c r="D30" s="10" t="n">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+188181
+</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>716.2</v>
       </c>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="10" t="n">
-        <v>90.59999999999999</v>
+      <c r="E30" s="11" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>966.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43</v>
+        <v>4570</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>6661.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>11565.6</v>
+        <v>26.6</v>
       </c>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="L30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n">
+        <v>719.7</v>
+      </c>
       <c r="M30" s="3" t="n">
-        <v>77.3</v>
+        <v>0.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>71.7</v>
+        <v>4.1</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>20.1</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1056.2</v>
+        <v>15.2</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>824.4</v>
       </c>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>248.1</v>
+        <v>246.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>14.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>3.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2999,15 +3042,15 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E31" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3022,51 +3065,49 @@
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="N31" s="8" t="n">
-        <v>170.5</v>
+      <c r="N31" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>21</v>
+        <v>2.1</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>72.3</v>
-      </c>
+      <c r="S31" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>17.7</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="n">
-        <v>88.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3082,59 +3123,61 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D32" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>83.09999999999999</v>
+      <c r="F32" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.7</v>
+        <v>0.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.3</v>
+        <v>1.3</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
+        <v>445.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>17</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>17</v>
+      <c r="S32" s="8" t="n">
+        <v>90</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>90</v>
+        <v>51.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>15.9</v>
@@ -3143,11 +3186,17 @@
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+710
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3163,76 +3212,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>235.5</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>24.9</v>
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>88.2</v>
+      <c r="F33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>78.59999999999999</v>
+        <v>1.7</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L33" s="8" t="n">
+      <c r="K33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="8" t="n">
-        <v>24.8</v>
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>51.5</v>
       </c>
-      <c r="U33" s="8" t="n">
-        <v>114.4</v>
+      <c r="U33" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>18</v>
+        <v>11.6</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3250,20 +3299,23 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="E34" s="12" t="n">
-        <v>0.6</v>
+      <c r="E34" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112179 1
+</t>
+        </is>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.5</v>
@@ -3272,49 +3324,57 @@
         <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>1.8</v>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>23.9</v>
+        <v>15.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S34" s="8" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>56.8</v>
+        <v>714.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V34" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="Y34" s="3" t="n">
-        <v>21</v>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+247
+</t>
+        </is>
       </c>
       <c r="Z34" s="3" t="n">
         <v>4.2</v>
@@ -3333,22 +3393,22 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>12.9</v>
+        <v>492.8</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>2.4</v>
@@ -3357,49 +3417,53 @@
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14181
+60
+</t>
+        </is>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>84.5</v>
+      <c r="Q35" s="8" t="n">
+        <v>45.7</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.5</v>
+        <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.9</v>
+        <v>56.8</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>20.7</v>
+        <v>206.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.8</v>
+        <v>79.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3420,26 +3484,26 @@
       <c r="C36" s="3" t="n">
         <v>498.9</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="G36" s="8" t="n">
+      <c r="E36" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="I36" s="3" t="n">
-        <v>2.2</v>
+      <c r="I36" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
@@ -3448,31 +3512,29 @@
         <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>11.5</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>91</v>
+        <v>918</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>14.1</v>
+        <v>44.1</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>11</v>
+      <c r="S36" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>55.1</v>
+        <v>60.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.2</v>
+        <v>1.2</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3480,14 +3542,14 @@
       <c r="W36" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>16.6</v>
+      <c r="X36" s="8" t="n">
+        <v>66.09999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3503,74 +3565,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2492.3</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>98.59999999999999</v>
+        <v>928</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>53.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>61.9</v>
+        <v>613.9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1110.6</v>
+        <v>1.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>48.5</v>
+        <v>0.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>121.8</v>
+        <v>12.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>7.2</v>
-      </c>
+        <v>75.7</v>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>149</v>
+        <v>4498</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>113.4</v>
+        <v>11.3</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>81.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>434.4</v>
+        <v>58.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
+        <v>4.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>7.1</v>
+        <v>377.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>809.8</v>
+        <v>804.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="Y37" s="3" t="n"/>
+        <v>85.2</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Z37" s="3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3586,62 +3646,71 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="11" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>18.5</v>
+      <c r="F38" s="11" t="n">
+        <v>1.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>2.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>11.8</v>
+        <v>89.90000000000001</v>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>17.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+14
+</t>
+        </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>17</v>
+        <v>84.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>11</v>
-      </c>
+        <v>31.4</v>
+      </c>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -3649,7 +3718,7 @@
         <v>16.1</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>81.90000000000001</v>
@@ -3671,74 +3740,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>395.5</v>
+        <v>58.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F39" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>23.5</v>
+        <v>7.1</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>71.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.9</v>
+        <v>5.7</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>50.1</v>
+        <v>5</v>
       </c>
       <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n">
-        <v>89.8</v>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+8917
+</t>
+        </is>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>25.8</v>
+      <c r="Q39" s="8" t="n">
+        <v>53.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>7.7</v>
+        <v>11.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52</v>
+        <v>64.7</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>191.1</v>
+        <v>1</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>11.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3754,73 +3827,77 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5452.1</v>
+        <v>545.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E40" s="11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>3</v>
+      <c r="I40" s="8" t="n">
+        <v>353</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>48.1</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>13.6</v>
+        <v>353.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>21</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+6
+</t>
+        </is>
       </c>
       <c r="P40" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.8</v>
+        <v>1.1</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>12</v>
+      <c r="U40" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>16</v>
+      <c r="W40" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>2.8</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>6.2</v>
@@ -3844,23 +3921,23 @@
       <c r="D41" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>10.8</v>
+      <c r="F41" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>14</v>
+        <v>24.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3868,26 +3945,26 @@
       <c r="L41" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>38.9</v>
+      <c r="M41" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>8770.1</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>80.8</v>
+      <c r="Q41" s="8" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>62.5</v>
@@ -3895,11 +3972,11 @@
       <c r="U41" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>19</v>
+      <c r="V41" s="8" t="n">
+        <v>96</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>17</v>
+        <v>658.5</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3926,75 +4003,82 @@
       <c r="C42" s="3" t="n">
         <v>340.1</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F42" s="11" t="n">
+      <c r="D42" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+181
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H42" s="8" t="n">
+      <c r="G42" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>14.6</v>
+      <c r="J42" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>621.1</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 111
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
 </t>
         </is>
       </c>
+      <c r="O42" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="P42" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="8" t="n">
-        <v>67.09999999999999</v>
+      <c r="R42" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>60.5</v>
+        <v>6.5</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>89.8</v>
+        <v>15.1</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>53.7</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4010,76 +4094,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5310.9</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>18.1</v>
+        <v>57</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>80.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>10</v>
+      <c r="K43" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="L43" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X43" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>16.2</v>
-      </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4095,25 +4179,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>857.1</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>18</v>
+        <v>5.1</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>18.25</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H44" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>14.6</v>
+        <v>2.6</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>5</v>
@@ -4121,20 +4205,24 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>89.59999999999999</v>
+      <c r="L44" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>91.8</v>
+        <v>40.9</v>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+1272971
+</t>
+        </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
@@ -4143,28 +4231,28 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="U44" s="8" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="V44" s="3" t="n">
-        <v>18.1</v>
+      <c r="V44" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>14.8</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>66.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>724</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4180,75 +4268,75 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>228.3</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>10.5</v>
+        <v>283</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>12.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>621</v>
+        <v>61</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.9</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>25.2</v>
+        <v>215.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>898.5</v>
+        <v>28.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>851.1</v>
+        <v>887.1</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>540.9</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>975.6</v>
+        <v>979.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>3561.1</v>
+        <v>351.1</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>95.8</v>
+        <v>0.6</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>9292.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+        <v>7.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4265,16 +4353,18 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4286,18 +4376,18 @@
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>14.1</v>
+      </c>
+      <c r="M46" s="3" t="n"/>
       <c r="N46" s="3" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.8</v>
@@ -4305,29 +4395,27 @@
       <c r="Q46" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>71.8</v>
+      <c r="R46" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
+        <v>0.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>18.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="n">
-        <v>15.9</v>
+        <v>0.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>27.8</v>
+        <v>7.8</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -772,32 +772,46 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.3</v>
+        <v>582.9</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="F4" s="9" t="inlineStr"/>
+      <c r="F4" s="11" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G4" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+        <v>13.1</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="L4" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25</v>
@@ -808,11 +822,17 @@
       <c r="S4" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>120.7</v>
+      </c>
       <c r="W4" s="3" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -831,37 +851,55 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="12" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F5" s="9" t="inlineStr"/>
+        <v>288.9</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G5" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="L5" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>16.7</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
@@ -872,13 +910,15 @@
       <c r="V5" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="n">
+        <v>75.5</v>
+      </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
       </c>
@@ -896,32 +936,56 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2508.9</v>
-      </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
-        <v>13.6</v>
+        <v>508.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>13.8</v>
+      </c>
       <c r="M6" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
@@ -929,16 +993,20 @@
         <v>10.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W6" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W6" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="X6" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -955,51 +1023,73 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="3" t="n">
+      <c r="D7" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>13.2</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>18.8</v>
+      <c r="F7" s="11" t="n">
+        <v>18.98</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>41</v>
+        <v>593</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>191.8</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
-      <c r="W7" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1016,17 +1106,21 @@
       <c r="C8" s="3" t="n">
         <v>229.8</v>
       </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="D8" s="9" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>17.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="I8" s="3" t="n">
         <v>1.8</v>
       </c>
@@ -1034,7 +1128,7 @@
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>7.7</v>
+        <v>27.2</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
@@ -1042,24 +1136,36 @@
       <c r="M8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="T8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="inlineStr"/>
@@ -1083,55 +1189,71 @@
         <v>118.5</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>269.4</v>
+        <v>881.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>116.4</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+        <v>31.1</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>60.7</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>14.6</v>
+        <v>86</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>459</v>
+        <v>959</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1114</v>
+        <v>1194</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>2162.6</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>959</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>17.9</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>419.8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1145,45 +1267,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="inlineStr"/>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="n">
+        <v>449</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>459</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
+        <v>91.8</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="R10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>62.9</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>530.1</v>
+        <v>10.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>90.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>89.7</v>
+        <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1199,53 +1351,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9445</v>
+        <v>221.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.7</v>
+        <v>22.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>13.5</v>
+        <v>19.7</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="L11" s="3" t="n">
-        <v>14.7</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q11" s="3" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="R11" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="U11" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W11" s="3" t="n">
@@ -1272,57 +1434,77 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>291.8</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>22.4</v>
+      </c>
       <c r="E12" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G12" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>92.8</v>
+      </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>19</v>
+        <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>188.4</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.9</v>
+        <v>6.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr"/>
-      <c r="Y12" s="3" t="inlineStr"/>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1336,56 +1518,78 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="G13" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>13</v>
+        <v>28.1</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>15.7</v>
+      </c>
       <c r="L13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="n">
-        <v>17.7</v>
+        <v>1.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.9</v>
+        <v>90.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1399,45 +1603,77 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="n">
-        <v>11.4</v>
+      <c r="C14" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="n">
+        <v>26.8</v>
+      </c>
       <c r="L14" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>13.7</v>
+      </c>
       <c r="N14" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y14" s="3" t="n">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1452,45 +1688,75 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>78.3</v>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="M15" s="3" t="n">
-        <v>13.7</v>
+        <v>148.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O15" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>96.8</v>
+      </c>
       <c r="P15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="W15" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
+        <v>15.7</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="Z15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1505,48 +1771,78 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>1972.2</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>91.09999999999999</v>
+      </c>
       <c r="G16" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+        <v>47.4</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="K16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>46.8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
       <c r="N16" s="3" t="n">
-        <v>18.5</v>
+        <v>1164.2</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="P16" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>88.40000000000001</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>164.8</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>16.6</v>
+        <v>84.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>180.6</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>488.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1561,74 +1857,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1972.2</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>47.4</v>
+        <v>225</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>16464.6</v>
-      </c>
-      <c r="O17" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>92.90000000000001</v>
+      </c>
       <c r="P17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>88</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>324.5</v>
+        <v>18.9</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>24.2</v>
+        <v>9</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>718.6</v>
+        <v>16.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2420.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1644,54 +1942,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>12.9</v>
+        <v>428.8</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>34.6</v>
+        <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>416.1</v>
+        <v>18.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="V18" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>81.8</v>
+      </c>
       <c r="Z18" s="3" t="n">
         <v>2</v>
       </c>
@@ -1709,54 +2027,74 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>428.5</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>840.6</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="T19" s="3" t="n">
-        <v>169.1</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>8</v>
+        <v>54</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="V19" s="3" t="inlineStr"/>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>4</v>
+        <v>27.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1772,47 +2110,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2440.6</v>
+        <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
+        <v>24.9</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="G20" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O20" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y20" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -1827,45 +2195,77 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>153.1</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="K21" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O21" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
+        <v>90.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T21" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="8" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="Z21" s="3" t="inlineStr"/>
+        <v>880.9</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -1880,52 +2280,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1261.7</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>123.3</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>9.9</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Q22" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="n">
-        <v>18.9</v>
+        <v>20.4</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="V22" s="3" t="inlineStr"/>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>870.9</v>
+        <v>94.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1941,58 +2365,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>123.3</v>
+        <v>1921.2</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="E23" s="11" t="inlineStr"/>
+        <v>11153.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>49.4</v>
+      </c>
       <c r="F23" s="10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+        <v>940.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>43.1</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="K23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
+        <v>38.2</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>122.1</v>
+      </c>
       <c r="N23" s="3" t="n">
-        <v>1.6</v>
+        <v>816.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>91.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>88.8</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>117.8</v>
+        <v>90</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>74</v>
+        <v>347.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>40.6</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>911.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1.8</v>
+        <v>113.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2008,74 +2450,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1983.2</v>
+        <v>215.4</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>43.7</v>
+        <v>22.6</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>644.4</v>
+        <v>69.8</v>
       </c>
       <c r="I24" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>7162.1</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>461.8</v>
-      </c>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>347.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>406.4</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>198.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2091,54 +2535,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>235.4</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
+        <v>490.4</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="G25" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>849.2</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>910.8</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S25" s="3" t="n">
+      <c r="X25" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
       </c>
@@ -2156,53 +2620,77 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>490.4</v>
+        <v>287.8</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+        <v>23.5</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="F26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>8.9</v>
+      </c>
       <c r="H26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="8" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="n">
-        <v>16.6</v>
-      </c>
       <c r="W26" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>16.2</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2216,50 +2704,78 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>2305.9</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="F27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>21.9</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>3.9</v>
+        <v>10.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M27" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N27" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2273,50 +2789,78 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
+        <v>2023.9</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>21.9</v>
+      </c>
       <c r="E28" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>13.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>24.2</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="N28" s="3" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q28" s="3" t="inlineStr"/>
-      <c r="R28" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="S28" s="3" t="n">
-        <v>19.9</v>
+        <v>17.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U28" s="3" t="inlineStr"/>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>72.8</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2331,47 +2875,77 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+        <v>289.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="G29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>82.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="K29" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="N29" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="P29" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2386,51 +2960,77 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>289.8</v>
+        <v>1682.9</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="E30" s="11" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+        <v>1120.9</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>43.7</v>
+      </c>
       <c r="H30" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>456.6</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>20021.4</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>561.9</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="X30" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="I30" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="n">
-        <v>182200.9</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="n">
+        <v>441.8</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>112.2</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2445,70 +3045,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1609.9</v>
+        <v>322</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>22.5</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>22.8</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="O31" s="3" t="n">
-        <v>42034.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>5.4</v>
+        <v>1</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>361.1</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>9491</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>7.1</v>
+        <v>941.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2524,57 +3130,77 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>18.1</v>
+        <v>482.8</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="G32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>14.9</v>
+      </c>
       <c r="N32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>895</v>
+      </c>
       <c r="P32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>81</v>
+      <c r="R32" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>901.1</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>14.9</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2588,57 +3214,77 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr"/>
-      <c r="G33" s="3" t="n">
-        <v>8.9</v>
+      <c r="C33" s="3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="P33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="8" t="n">
-        <v>17</v>
+      <c r="Q33" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="S33" s="8" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V33" s="3" t="inlineStr"/>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>31.9</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>40.6</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>195</v>
+        <v>71.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -2653,49 +3299,77 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="8" t="n">
-        <v>11.5</v>
+      <c r="C34" s="3" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>11.36</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>19.7</v>
+        <v>12.6</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="T34" s="3" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V34" s="3" t="inlineStr"/>
-      <c r="W34" s="3" t="inlineStr"/>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>26.8</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Y34" s="3" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.8</v>
+        <v>89.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -2710,47 +3384,77 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="E35" s="8" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
+        <v>9180</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T35" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
-      <c r="X35" s="3" t="inlineStr"/>
-      <c r="Y35" s="3" t="inlineStr"/>
+        <v>600.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>1424.8</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>75.5</v>
+      </c>
       <c r="Z35" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -2765,45 +3469,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>498.3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>13.9</v>
+      </c>
       <c r="F36" s="3" t="n">
-        <v>19.1</v>
+        <v>12.1</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
+      <c r="Q36" s="8" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="U36" s="3" t="inlineStr"/>
+        <v>552.1</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>1424.8</v>
+      </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>79.8</v>
+      </c>
       <c r="Z36" s="3" t="n">
         <v>4.5</v>
       </c>
@@ -2821,61 +3555,73 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1182.8</v>
+        <v>122.8</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="E37" s="11" t="inlineStr"/>
+        <v>124.2</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>825.8</v>
+      </c>
       <c r="F37" s="10" t="n">
-        <v>928.6</v>
+        <v>22.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+        <v>22.9</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
+        <v>110.8</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>122.9</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>1.3</v>
+        <v>29.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>8012</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>9449</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q37" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>113.4</v>
+      </c>
       <c r="R37" s="3" t="n">
-        <v>81.8</v>
+        <v>1</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>284.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>312.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1291</v>
+        <v>21</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>50.4</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.2</v>
+        <v>82</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>909.2</v>
+        <v>940.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>128.1</v>
@@ -2896,51 +3642,75 @@
       <c r="C38" s="3" t="n">
         <v>9438.6</v>
       </c>
-      <c r="D38" s="11" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
+      <c r="D38" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>12.2</v>
+      </c>
       <c r="F38" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H38" s="3" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
-        <v>45.4</v>
+        <v>23.2</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="n">
+        <v>22.7</v>
+      </c>
       <c r="R38" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
+        <v>17.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="V38" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>464.1</v>
-      </c>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2955,55 +3725,77 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1395.3</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F39" s="8" t="n">
+        <v>395</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>12.8</v>
+      <c r="H39" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y39" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="n">
+        <v>16.4</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3018,44 +3810,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4034.4</v>
-      </c>
-      <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
+        <v>2942.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="F40" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="n">
-        <v>3</v>
+      <c r="G40" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="L40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="8" t="n">
+        <v>299.5</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="inlineStr"/>
-      <c r="X40" s="3" t="inlineStr"/>
-      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="Z40" s="3" t="n">
-        <v>16.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3071,52 +3893,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>2.2</v>
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
+        <v>4.7</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="3" t="n">
-        <v>69.8</v>
+        <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr"/>
+      <c r="Q41" s="8" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>162.5</v>
+      </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3132,50 +3976,70 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1337</v>
-      </c>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
+        <v>349.1</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="H42" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="3" t="n">
-        <v>10.4</v>
+        <v>11.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="inlineStr"/>
-      <c r="R42" s="3" t="inlineStr"/>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>1460.5</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="V42" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="n">
-        <v>81.8</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>98.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3191,52 +4055,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
+        <v>517</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E43" s="12" t="inlineStr"/>
       <c r="F43" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>19.7</v>
+      </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L43" s="3" t="n">
-        <v>1.4</v>
+        <v>16.2</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="n">
-        <v>18.7</v>
+        <v>82</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.9</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>959.3</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
+        <v>81.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>85</v>
+        <v>3.7</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3252,18 +4138,24 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22830.1</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+        <v>653.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="F44" s="3" t="n">
         <v>18</v>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="J44" s="3" t="n">
         <v>5</v>
       </c>
@@ -3271,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>1.4</v>
+        <v>13.6</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
@@ -3280,33 +4172,29 @@
       <c r="O44" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="n">
-        <v>18.7</v>
+      <c r="P44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>959.3</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>28.7</v>
-      </c>
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -3321,54 +4209,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>22830.1</v>
+        <v>2283</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>191.7</v>
-      </c>
-      <c r="E45" s="11" t="inlineStr"/>
-      <c r="F45" s="11" t="inlineStr"/>
+        <v>198.5</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>110.2</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>10.8</v>
+        <v>128.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>91.8</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
-      </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
+        <v>290.9</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>104.1</v>
+      </c>
       <c r="S45" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="3" t="inlineStr"/>
+        <v>99.8</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>169</v>
+      </c>
       <c r="V45" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>95.8</v>
+        <v>220.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>4648.4</v>
+      </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3384,57 +4294,77 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>29497</v>
+        <v>498</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>254.1</v>
+      </c>
       <c r="P46" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V46" s="3" t="n">
-        <v>212.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="X46" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,10 +152,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -772,15 +775,15 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.9</v>
+        <v>582.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25.1</v>
+        <v>8.4</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -790,13 +793,13 @@
         <v>13.1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>45.1</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.2</v>
+        <v>1.2</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>11.7</v>
@@ -805,7 +808,7 @@
         <v>13.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -823,16 +826,14 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>120.7</v>
+        <v>52</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="n">
+        <v>107.1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -851,46 +852,46 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>288.9</v>
+        <v>388.5</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>10.8</v>
+        <v>29.1</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>14.2</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.3</v>
+      <c r="H5" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.4</v>
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
@@ -917,7 +918,7 @@
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -944,8 +945,8 @@
       <c r="E6" s="11" t="n">
         <v>12.8</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>18</v>
+      <c r="F6" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.2</v>
@@ -962,14 +963,14 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>13</v>
+      <c r="M6" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
@@ -978,7 +979,7 @@
         <v>1.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
@@ -995,17 +996,17 @@
       <c r="V6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="8" t="n">
-        <v>18.1</v>
+      <c r="X6" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1026,69 +1027,67 @@
       <c r="D7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>18.98</v>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>18.8</v>
+      <c r="M7" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>52.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>593</v>
+        <v>293</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.1</v>
+        <v>21</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1106,13 +1105,13 @@
       <c r="C8" s="3" t="n">
         <v>229.8</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>41.9</v>
+      <c r="D8" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1128,7 +1127,7 @@
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>27.2</v>
+        <v>6.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
@@ -1137,10 +1136,10 @@
         <v>14.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1151,14 +1150,14 @@
       <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>3.8</v>
+        <v>35.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
@@ -1185,71 +1184,69 @@
       <c r="C9" s="3" t="n">
         <v>2224.9</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>118.5</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="E9" s="9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>881.5</v>
+        <v>20.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>10.5</v>
-      </c>
+        <v>63.1</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
+        <v>260.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>19.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>60.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>86</v>
+        <v>16.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>959</v>
+        <v>1590.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1194</v>
+        <v>114</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>6.8</v>
+        <v>86.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2162.6</v>
+        <v>212.6</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>959</v>
+        <v>94</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>419.8</v>
+        <v>848.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2</v>
@@ -1268,15 +1265,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>449</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>495</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1286,12 +1283,14 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>3.8</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>14.7</v>
       </c>
@@ -1302,22 +1301,22 @@
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>91.8</v>
+        <v>921.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.3</v>
+        <v>113.8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>85.8</v>
+        <v>9</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>17.2</v>
+      <c r="S10" s="8" t="n">
+        <v>78.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1351,58 +1350,58 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>221.8</v>
+        <v>924.2</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>10.8</v>
+      <c r="K11" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>10.4</v>
+        <v>885</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="S11" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>28.4</v>
+        <v>82</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>10.6</v>
@@ -1446,7 +1445,7 @@
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>9.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>13</v>
@@ -1461,16 +1460,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>11.4</v>
+        <v>14.5</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>83.5</v>
+        <v>38.5</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.8</v>
+        <v>12.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1491,7 +1490,7 @@
         <v>6.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>16</v>
+        <v>1.6</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>14.8</v>
@@ -1500,7 +1499,7 @@
         <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>240.8</v>
+        <v>18.4</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>3.8</v>
@@ -1527,14 +1526,14 @@
       <c r="E13" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>18.8</v>
+      <c r="F13" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>28.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1546,7 +1545,7 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
@@ -1558,7 +1557,7 @@
         <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>15.8</v>
@@ -1567,10 +1566,10 @@
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.2</v>
@@ -1582,10 +1581,10 @@
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.8</v>
@@ -1609,26 +1608,26 @@
       <c r="D14" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>17.8</v>
+        <v>11.4</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.5</v>
+        <v>71.5</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>21.4</v>
+        <v>11.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>26.8</v>
+        <v>86.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1646,22 +1645,22 @@
         <v>1</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.3</v>
+        <v>2.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>14.8</v>
@@ -1695,11 +1694,11 @@
       <c r="E15" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>78.3</v>
+      <c r="F15" s="3" t="n">
+        <v>7.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>12.6</v>
@@ -1708,7 +1707,7 @@
         <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>5.9</v>
@@ -1717,7 +1716,7 @@
         <v>14.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>148.1</v>
+        <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
@@ -1726,7 +1725,7 @@
         <v>96.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
@@ -1772,73 +1771,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1972.2</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1973.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>91.09999999999999</v>
+      <c r="E16" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>47.4</v>
+        <v>17.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>649.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>191.2</v>
+        <v>73.2</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1164.2</v>
+        <v>15.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>64.8</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.8</v>
+        <v>61.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>164.8</v>
+        <v>3945.2</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>180.6</v>
+        <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>488.8</v>
+        <v>428.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>2.8</v>
@@ -1857,19 +1856,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>1469.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>41.8</v>
+      <c r="E17" s="9" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1877,11 +1876,11 @@
       <c r="I17" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
@@ -1890,7 +1889,7 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1902,16 +1901,16 @@
         <v>19.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>18.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>16.9</v>
@@ -1944,38 +1943,38 @@
       <c r="C18" s="3" t="n">
         <v>428.8</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>2.4</v>
+      <c r="D18" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>16.2</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.4</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>10.1</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>14.4</v>
+        <v>19.4</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
@@ -1984,7 +1983,7 @@
         <v>1.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>21.8</v>
+        <v>64.5</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>17.8</v>
@@ -1999,13 +1998,13 @@
         <v>8</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>16.9</v>
+        <v>18.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>81.8</v>
@@ -2027,10 +2026,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>840.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>1.5</v>
+        <v>440.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>14</v>
@@ -2039,13 +2038,13 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
@@ -2060,7 +2059,7 @@
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>11.5</v>
+        <v>46.4</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
@@ -2069,7 +2068,7 @@
         <v>11.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.1</v>
@@ -2080,21 +2079,23 @@
       <c r="T19" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>16.8</v>
+        <v>4.9</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>18.8</v>
+        <v>185.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>27.4</v>
+        <v>127.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2113,22 +2114,22 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>17.8</v>
+      <c r="F20" s="13" t="n">
+        <v>1.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.4</v>
@@ -2152,10 +2153,10 @@
         <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.6</v>
+        <v>2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2164,13 +2165,13 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>14.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>16.8</v>
+        <v>75.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>18.6</v>
@@ -2203,32 +2204,32 @@
       <c r="E21" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>1.8</v>
+      <c r="F21" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>11.9</v>
+        <v>7.2</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>16.4</v>
+      <c r="L21" s="8" t="n">
+        <v>56.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1</v>
+        <v>121.3</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2236,22 +2237,22 @@
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>18.9</v>
+        <v>43.1</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>74</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2282,41 +2283,41 @@
       <c r="C22" s="3" t="n">
         <v>123.3</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>94.40000000000001</v>
+      <c r="D22" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>11.6</v>
+      <c r="N22" s="8" t="n">
+        <v>68.90000000000001</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2331,13 +2332,13 @@
         <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>74</v>
+        <v>740.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2349,7 +2350,7 @@
         <v>94.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2365,43 +2366,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1921.2</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>11153.1</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>940.8</v>
+        <v>477.4</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>43.1</v>
+        <v>2654</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>69.8</v>
+        <v>636.4</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>80.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>38.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16.1</v>
+        <v>161.4</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>122.1</v>
+        <v>14.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>816.4</v>
+        <v>31.6</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1</v>
@@ -2413,7 +2414,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2422,19 +2423,19 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>918.9</v>
+        <v>919.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>911.8</v>
+        <v>942.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>48.4</v>
+        <v>148.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2452,20 +2453,20 @@
       <c r="C24" s="3" t="n">
         <v>215.4</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>69.8</v>
+        <v>636.4</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2477,13 +2478,13 @@
         <v>38.2</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>15.2</v>
+        <v>45.9</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>92.40000000000001</v>
@@ -2501,7 +2502,7 @@
         <v>18.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>8.1</v>
@@ -2509,11 +2510,11 @@
       <c r="V24" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2535,40 +2536,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>490.4</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.6</v>
+        <v>130.4</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>64.31</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>15</v>
+        <v>18.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>12.8</v>
+      <c r="H25" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>18.1</v>
+      <c r="J25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.1</v>
+        <v>15.1</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>849.2</v>
+        <v>34.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>910.8</v>
@@ -2576,17 +2577,17 @@
       <c r="P25" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q25" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q25" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>8</v>
@@ -2594,8 +2595,8 @@
       <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>12.9</v>
+      <c r="W25" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>18.1</v>
@@ -2620,7 +2621,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>287.8</v>
+        <v>87.8</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>23.5</v>
@@ -2635,19 +2636,19 @@
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>5.9</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>14.9</v>
@@ -2659,10 +2660,10 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.7</v>
+        <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>17.3</v>
@@ -2677,19 +2678,19 @@
         <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>88.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2705,16 +2706,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2305.9</v>
+        <v>5.9</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18.9</v>
+        <v>14.1</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
@@ -2723,22 +2724,22 @@
         <v>14.9</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>21.9</v>
+        <v>1.2</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2752,11 +2753,11 @@
       <c r="R27" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>5.6</v>
@@ -2765,7 +2766,7 @@
         <v>17.8</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
@@ -2790,7 +2791,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2023.9</v>
+        <v>305.9</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>21.9</v>
@@ -2798,38 +2799,38 @@
       <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>11.79</v>
+      <c r="F28" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>65.40000000000001</v>
+        <v>1.1</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.5</v>
@@ -2844,7 +2845,7 @@
         <v>72.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.7</v>
@@ -2877,44 +2878,44 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.1</v>
+        <v>84.5</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L29" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.5</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>21.7</v>
@@ -2926,7 +2927,7 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
@@ -2960,15 +2961,15 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1682.9</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1120.9</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F30" s="10" t="n">
+        <v>1689.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1129.8</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2978,58 +2979,58 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>456.6</v>
+        <v>38.6</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>71.8</v>
+        <v>1.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>20021.4</v>
+        <v>479.8</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>20.5</v>
+        <v>105.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.9</v>
+        <v>561.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>394.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>88</v>
+        <v>18.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>18.8</v>
+        <v>88</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>441.8</v>
+        <v>416.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>112.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3047,20 +3048,20 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E31" s="10" t="n">
+      <c r="D31" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>22.8</v>
+        <v>28.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3069,16 +3070,16 @@
         <v>1.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>38.6</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.3</v>
+        <v>1.4</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>94.09999999999999</v>
@@ -3096,10 +3097,10 @@
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v>16.3</v>
+        <v>116.3</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17.6</v>
@@ -3111,10 +3112,10 @@
         <v>17.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.8</v>
+        <v>88.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>941.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3130,67 +3131,67 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>482.8</v>
+        <v>481.8</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="E32" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>11.9</v>
+      <c r="E32" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>105.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>895</v>
+        <v>83</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>901.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.7</v>
@@ -3215,46 +3216,46 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>89.7</v>
+        <v>422.8</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>6618.45</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>11.7</v>
+        <v>91.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>1.2</v>
+        <v>16.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>15.8</v>
+      <c r="N33" s="8" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3263,25 +3264,25 @@
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="X33" s="8" t="n">
-        <v>40.6</v>
+        <v>13.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3302,56 +3303,56 @@
       <c r="C34" s="3" t="n">
         <v>492.8</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E34" s="9" t="n">
-        <v>11.36</v>
+      <c r="E34" s="13" t="n">
+        <v>3.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>8.300000000000001</v>
+      <c r="H34" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>23.1</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>11.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>26.8</v>
+        <v>56.8</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.8</v>
@@ -3360,16 +3361,14 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>16.7</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>89.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3385,16 +3384,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>11</v>
+        <v>24.2</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>13.3</v>
+      <c r="F35" s="13" t="n">
+        <v>4.4</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>89.40000000000001</v>
@@ -3409,45 +3408,45 @@
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>13.5</v>
+      <c r="M35" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.7</v>
+        <v>17.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>9180</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>18.8</v>
+        <v>2</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>1424.8</v>
+        <v>60</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
@@ -3478,17 +3477,17 @@
       <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
+      <c r="F36" s="13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3502,8 +3501,8 @@
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>18.9</v>
+      <c r="N36" s="8" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3511,20 +3510,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>124.2</v>
+      <c r="Q36" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>71</v>
+      <c r="S36" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>552.1</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>1424.8</v>
+        <v>55.1</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3555,76 +3554,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>825.8</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>22.6</v>
+        <v>128.1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4</v>
+        <v>18.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.8</v>
+        <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>122.9</v>
+        <v>121.8</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>29.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>8012</v>
+        <v>15.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>19.1</v>
+        <v>11.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>449</v>
+        <v>44930.3</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>113.4</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>940.2</v>
+        <v>41252.4</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3640,46 +3639,46 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9438.6</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>438.6</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="L38" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>52.1</v>
+        <v>58.1</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>89.8</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>22.7</v>
@@ -3688,10 +3687,10 @@
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>17</v>
+        <v>480.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62.1</v>
+        <v>63.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3700,16 +3699,16 @@
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>16.1</v>
+        <v>15.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>224.9</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3725,40 +3724,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>92</v>
+        <v>2392.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>15.9</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>52.1</v>
+        <v>1.5</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
@@ -3766,35 +3765,35 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>19.6</v>
+      <c r="Q39" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52.8</v>
+        <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>71</v>
+        <v>14</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>1.9</v>
+        <v>12.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>11.8</v>
+        <v>71</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>16.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3812,42 +3811,40 @@
       <c r="C40" s="3" t="n">
         <v>2942.1</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>18.8</v>
+      <c r="D40" s="13" t="n">
+        <v>49.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>19.1</v>
+        <v>13.8</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>4.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P40" s="3" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>299.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>25.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>23.8</v>
@@ -3859,7 +3856,7 @@
         <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>68.5</v>
+        <v>58.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
@@ -3868,7 +3865,7 @@
         <v>19.4</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>16</v>
+        <v>12.1</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>16.8</v>
@@ -3898,20 +3895,20 @@
       <c r="D41" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>11.1</v>
+      <c r="G41" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>11.1</v>
+        <v>81</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4.7</v>
@@ -3923,35 +3920,35 @@
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.6</v>
+        <v>1.3</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>123.9</v>
+      <c r="Q41" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>162.5</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3960,7 +3957,7 @@
         <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3976,22 +3973,24 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>349.1</v>
-      </c>
-      <c r="D42" s="8" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F42" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F42" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J42" s="3" t="n">
         <v>4</v>
       </c>
@@ -3999,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.4</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>14.6</v>
@@ -4014,16 +4013,16 @@
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>43.4</v>
+        <v>18</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>1460.5</v>
+        <v>60.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>10.4</v>
@@ -4055,41 +4054,41 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>517</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0.1</v>
+        <v>537</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>49.5</v>
       </c>
       <c r="E43" s="12" t="inlineStr"/>
       <c r="F43" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>11.4</v>
+      <c r="G43" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>19.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>21.1</v>
+        <v>8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>4.4</v>
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>2</v>
@@ -4097,23 +4096,23 @@
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="8" t="n">
-        <v>16.5</v>
+      <c r="R43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0.2</v>
+        <v>11.2</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>16.2</v>
@@ -4138,7 +4137,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>653.1</v>
+        <v>223.1</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>23.4</v>
@@ -4163,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
@@ -4173,13 +4172,13 @@
         <v>91</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R44" s="8" t="n">
-        <v>68.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>13.9</v>
@@ -4188,7 +4187,7 @@
         <v>59.5</v>
       </c>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="W44" s="3" t="inlineStr"/>
@@ -4209,76 +4208,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2283</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>219.1</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>110.2</v>
+        <v>2282</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1981.8</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>110.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>128.8</v>
+        <v>20.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>26.2</v>
+        <v>286.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10.1</v>
+        <v>180.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>82.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.8</v>
+        <v>31.3</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>290.9</v>
+        <v>240.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>112.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>121.6</v>
+        <v>21</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>104.1</v>
+        <v>10.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>99.8</v>
+        <v>92.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>111.8</v>
+        <v>119.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>220.8</v>
+        <v>22</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>36</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>4648.4</v>
+        <v>966.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4294,15 +4293,15 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>498</v>
-      </c>
-      <c r="D46" s="10" t="n">
+        <v>497</v>
+      </c>
+      <c r="D46" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="E46" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F46" s="10" t="n">
+      <c r="E46" s="9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4317,23 +4316,21 @@
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N46" s="8" t="n">
-        <v>38.9</v>
+      <c r="N46" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>254.1</v>
+        <v>20.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>22.8</v>
@@ -4347,20 +4344,18 @@
       <c r="T46" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>87.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>4.8</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -819,7 +819,7 @@
       <c r="Q4" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -829,10 +829,10 @@
         <v>52</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="W4" s="3" t="n">
+      <c r="V4" s="13" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="W4" s="13" t="n">
         <v>1.6</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -896,7 +896,7 @@
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="11" t="n">
         <v>17.2</v>
       </c>
       <c r="S5" s="8" t="n">
@@ -981,7 +981,7 @@
       <c r="Q6" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1061,8 +1061,8 @@
       <c r="P7" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="n">
+      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="R7" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1147,7 +1147,7 @@
       <c r="Q8" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1203,13 +1203,13 @@
       <c r="J9" s="3" t="n">
         <v>260.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="9" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1221,10 +1221,10 @@
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>114</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="11" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1236,10 +1236,10 @@
       <c r="U9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>80.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1291,10 +1291,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1306,10 +1306,10 @@
       <c r="P10" s="3" t="n">
         <v>113.8</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1321,10 +1321,10 @@
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1376,7 +1376,7 @@
       <c r="K11" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="13" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
@@ -1409,7 +1409,7 @@
       <c r="V11" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1489,10 +1489,10 @@
       <c r="U12" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="13" t="n">
         <v>1.6</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1577,7 +1577,7 @@
       <c r="V13" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1644,7 +1644,7 @@
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="13" t="n">
         <v>2.8</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1662,7 +1662,7 @@
       <c r="V14" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1745,7 +1745,7 @@
       <c r="V15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1794,13 +1794,13 @@
       <c r="J16" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="9" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="9" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1812,10 +1812,10 @@
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>61.4</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1827,10 +1827,10 @@
       <c r="U16" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1882,10 +1882,10 @@
       <c r="K17" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1897,10 +1897,10 @@
       <c r="P17" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1912,10 +1912,10 @@
       <c r="U17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1964,7 +1964,7 @@
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
@@ -1982,7 +1982,7 @@
       <c r="P18" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="13" t="n">
         <v>64.5</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -2049,13 +2049,13 @@
       <c r="J19" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="11" t="n">
         <v>18.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="13" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2067,7 +2067,7 @@
       <c r="P19" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="13" t="n">
         <v>2.4</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2085,7 +2085,7 @@
       <c r="V19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="13" t="n">
         <v>4.9</v>
       </c>
       <c r="X19" s="8" t="n">
@@ -2134,7 +2134,7 @@
       <c r="J20" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="11" t="n">
         <v>5.6</v>
       </c>
       <c r="L20" s="8" t="n">
@@ -2152,10 +2152,10 @@
       <c r="P20" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="13" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2170,7 +2170,7 @@
       <c r="V20" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="13" t="n">
         <v>75.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2219,10 +2219,10 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="11" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="13" t="n">
         <v>56.2</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2304,7 +2304,7 @@
       <c r="J22" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
@@ -2389,13 +2389,13 @@
       <c r="J23" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>38.2</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="9" t="n">
         <v>161.4</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="9" t="n">
         <v>14.6</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2407,10 +2407,10 @@
       <c r="P23" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="9" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2422,10 +2422,10 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="9" t="n">
         <v>919.8</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2477,10 +2477,10 @@
       <c r="K24" s="3" t="n">
         <v>38.2</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>45.9</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="9" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2492,10 +2492,10 @@
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>47.8</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2507,10 +2507,10 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2562,7 +2562,7 @@
       <c r="K25" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="11" t="n">
         <v>15.1</v>
       </c>
       <c r="M25" s="8" t="n">
@@ -2577,10 +2577,10 @@
       <c r="P25" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="13" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="S25" s="8" t="n">
@@ -2592,10 +2592,10 @@
       <c r="U25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2647,7 +2647,7 @@
       <c r="K26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="11" t="n">
         <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
@@ -2662,7 +2662,7 @@
       <c r="P26" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="11" t="n">
         <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2677,10 +2677,10 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="11" t="n">
         <v>16.5</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2732,7 +2732,7 @@
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="11" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
@@ -2747,7 +2747,7 @@
       <c r="P27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="11" t="n">
         <v>20.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2762,10 +2762,10 @@
       <c r="U27" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2817,7 +2817,7 @@
       <c r="K28" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="11" t="n">
         <v>15.4</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2832,7 +2832,7 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="R28" s="3" t="n">
@@ -2847,10 +2847,10 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2902,10 +2902,10 @@
       <c r="K29" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="11" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="13" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2917,7 +2917,7 @@
       <c r="P29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="11" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
@@ -2932,10 +2932,10 @@
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="11" t="n">
         <v>17.1</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2984,13 +2984,13 @@
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>38.6</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3002,10 +3002,10 @@
       <c r="P30" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="9" t="n">
         <v>27.4</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3017,10 +3017,10 @@
       <c r="U30" s="3" t="n">
         <v>394.6</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="9" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3072,10 +3072,10 @@
       <c r="K31" s="3" t="n">
         <v>38.6</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="11" t="n">
         <v>14.9</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3087,10 +3087,10 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3102,10 +3102,10 @@
       <c r="U31" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3160,8 +3160,8 @@
       <c r="L32" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>105.1</v>
+      <c r="M32" s="13" t="n">
+        <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>16.1</v>
@@ -3187,7 +3187,7 @@
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3272,7 +3272,7 @@
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="11" t="n">
         <v>18</v>
       </c>
       <c r="W33" s="8" t="n">
@@ -3330,7 +3330,7 @@
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="13" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3345,7 +3345,7 @@
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="13" t="n">
         <v>1.7</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3357,7 +3357,7 @@
       <c r="U34" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="11" t="n">
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3440,10 +3440,10 @@
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="13" t="n">
         <v>1.7</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3525,7 +3525,7 @@
       <c r="U36" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3577,13 +3577,13 @@
       <c r="J37" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>121.8</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>15.6</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3595,10 +3595,10 @@
       <c r="P37" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3610,10 +3610,10 @@
       <c r="U37" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3665,10 +3665,10 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>15.1</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="8" t="n">
@@ -3680,10 +3680,10 @@
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3695,10 +3695,10 @@
       <c r="U38" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="9" t="n">
         <v>15.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3750,7 +3750,7 @@
       <c r="K39" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3780,7 +3780,7 @@
       <c r="U39" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="13" t="n">
         <v>1.9</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3830,7 +3830,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr"/>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
@@ -3919,7 +3919,7 @@
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="13" t="n">
         <v>1.3</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="13" t="n">
         <v>1.8</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="13" t="n">
         <v>1.5</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -4000,7 +4000,7 @@
       <c r="L42" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="13" t="n">
         <v>1.3</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4015,7 +4015,7 @@
       <c r="Q42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="13" t="n">
         <v>4.8</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4096,7 +4096,7 @@
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="13" t="n">
         <v>1.6</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4111,7 +4111,7 @@
       <c r="V43" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="13" t="n">
         <v>0.1</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4177,7 +4177,7 @@
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="13" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4190,7 +4190,7 @@
       <c r="V44" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4231,13 +4231,13 @@
       <c r="J45" s="3" t="n">
         <v>286.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>180.1</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>7</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4249,10 +4249,10 @@
       <c r="P45" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="9" t="n">
         <v>10.4</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4264,10 +4264,10 @@
       <c r="U45" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>119.8</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>22</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4317,10 +4317,10 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4332,10 +4332,10 @@
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4345,10 +4345,10 @@
         <v>58.5</v>
       </c>
       <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,16 +158,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,10 +784,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.2</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.4</v>
+        <v>25.1</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>13.6</v>
@@ -796,19 +805,19 @@
         <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M4" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M4" s="11" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>1.4</v>
+      <c r="N4" s="8" t="n">
+        <v>29.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -816,25 +825,25 @@
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="13" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="W4" s="13" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -852,10 +861,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.5</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>29.1</v>
+        <v>38.8</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>93.90000000000001</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>14.2</v>
@@ -866,59 +875,59 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>12.1</v>
+      <c r="H5" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M5" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="M5" s="11" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Q5" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="R5" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>16.7</v>
+      <c r="R5" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -937,7 +946,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>24.1</v>
@@ -946,13 +955,13 @@
         <v>12.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>11.8</v>
+        <v>18.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
@@ -961,34 +970,34 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>30.9</v>
+      <c r="M6" s="11" t="n">
+        <v>13.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>19.5</v>
+        <v>45.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>1.1</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.4</v>
@@ -996,17 +1005,17 @@
       <c r="V6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,46 +1036,50 @@
       <c r="D7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="n">
+        <v>13.2</v>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.4</v>
+        <v>2.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>52.1</v>
+      <c r="N7" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>293</v>
+        <v>52.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q7" s="12" t="inlineStr"/>
-      <c r="R7" s="11" t="n">
-        <v>17.6</v>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>12.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
@@ -1074,20 +1087,20 @@
       <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1106,7 +1119,7 @@
         <v>229.8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>13.8</v>
@@ -1121,53 +1134,59 @@
         <v>12.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>6.4</v>
+        <v>11.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>14.2</v>
+      <c r="M8" s="11" t="n">
+        <v>14.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>16.2</v>
+        <v>40.3</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>93</v>
+        <v>11.6</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1182,75 +1201,75 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2224.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1118.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20.9</v>
+        <v>30.9</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>63.1</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>706.4</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>260.5</v>
-      </c>
-      <c r="K9" s="9" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="10" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="M9" s="9" t="n">
-        <v>68.90000000000001</v>
+      <c r="M9" s="10" t="n">
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>16.6</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1590.1</v>
+        <v>59</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="11" t="n">
         <v>114</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="10" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.8</v>
+        <v>86.2</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>212.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="V9" s="10" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W9" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>848.1</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1265,15 +1284,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>495</v>
-      </c>
-      <c r="D10" s="9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D10" s="10" t="n">
         <v>23.7</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1283,58 +1302,56 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="10" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="11" t="n">
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>921.8</v>
+        <v>99.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R10" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="8" t="n">
-        <v>78.2</v>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.8</v>
+        <v>19.6</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="3" t="n">
         <v>83</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1350,75 +1367,77 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>924.2</v>
+        <v>191.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>1.2</v>
+        <v>10</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.1</v>
+        <v>11.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>885</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>20.8</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q11" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>1.1</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>82</v>
+        <v>140649.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>10.6</v>
+        <v>55.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>17.9</v>
+        <v>34.1</v>
+      </c>
+      <c r="W11" s="9" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>717.5</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>80494</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1433,19 +1452,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229</v>
+        <v>229.5</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>13</v>
@@ -1459,50 +1478,46 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>38.5</v>
+      <c r="L12" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>12.8</v>
+        <v>931.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="S12" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V12" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W12" s="11" t="n">
-        <v>14.8</v>
-      </c>
+        <v>24.8</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" s="13" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>17.5</v>
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>18.4</v>
+        <v>940.5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1548,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1545,21 +1560,21 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q13" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1569,22 +1584,22 @@
         <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="W13" s="11" t="n">
-        <v>15.8</v>
+        <v>16.9</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.8</v>
@@ -1606,28 +1621,28 @@
         <v>324</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E14" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>86.8</v>
+        <v>56.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1636,40 +1651,40 @@
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94</v>
+        <v>0.1</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="13" t="n">
-        <v>2.8</v>
+      <c r="Q14" s="11" t="n">
+        <v>21.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="V14" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W14" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.6</v>
@@ -1690,30 +1705,32 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="12" t="inlineStr"/>
+      <c r="D15" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7.5</v>
+        <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>13.8</v>
@@ -1722,12 +1739,12 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>96.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q15" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1740,22 +1757,22 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X15" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="Y15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="11" t="n">
+      <c r="Z15" s="3" t="n">
         <v>15.7</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1771,76 +1788,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1973.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>96</v>
+      <c r="E16" s="10" t="n">
+        <v>674.7</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>164.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="L16" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="L16" s="10" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="9" t="n">
-        <v>69.40000000000001</v>
+      <c r="M16" s="10" t="n">
+        <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>15.4</v>
+        <v>1140.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>61.4</v>
+      <c r="Q16" s="10" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>83</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>3945.2</v>
+        <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>18.6</v>
+        <v>24.2</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>428.8</v>
+        <v>1208.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1856,19 +1873,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1469.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>4.8</v>
+        <v>295</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1877,55 +1894,55 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="L17" s="9" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="9" t="n">
-        <v>13.9</v>
+      <c r="M17" s="10" t="n">
+        <v>19.1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.8</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R17" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q17" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R17" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.9</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2</v>
+        <v>15.3</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1941,51 +1958,49 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.8</v>
-      </c>
-      <c r="D18" s="3" t="n">
+        <v>428.3</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>18.1</v>
+      <c r="E18" s="11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
+      <c r="K18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.4</v>
+        <v>14.4</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q18" s="13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="R18" s="3" t="n">
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R18" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1995,22 +2010,22 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V18" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>16</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>17</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2028,49 +2043,49 @@
       <c r="C19" s="3" t="n">
         <v>440.6</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E19" s="3" t="n">
+      <c r="D19" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>13</v>
+      <c r="G19" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="9" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.4</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q19" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R19" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="R19" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2082,20 +2097,20 @@
       <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W19" s="13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>185.3</v>
+      <c r="V19" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="W19" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>127.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2113,50 +2128,50 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E20" s="3" t="n">
+      <c r="D20" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="13" t="n">
-        <v>1.7</v>
+      <c r="F20" s="11" t="n">
+        <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K20" s="11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>15.1</v>
+      <c r="L20" s="11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" s="13" t="n">
-        <v>87.59999999999999</v>
+        <v>9</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2165,13 +2180,13 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V20" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="13" t="n">
-        <v>75.5</v>
+      <c r="W20" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>18.6</v>
@@ -2198,20 +2213,20 @@
       <c r="C21" s="3" t="n">
         <v>261.7</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>19.9</v>
+        <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>11.1</v>
@@ -2219,32 +2234,32 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="13" t="n">
-        <v>56.2</v>
+      <c r="L21" s="11" t="n">
+        <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>121.3</v>
+        <v>11.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>90.8</v>
+        <v>99.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R21" s="3" t="n">
+      <c r="Q21" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R21" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>43.1</v>
+        <v>18.9</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>74</v>
@@ -2252,17 +2267,17 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>18.2</v>
+      <c r="V21" s="11" t="n">
+        <v>18.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>880.9</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>2.8</v>
@@ -2283,41 +2298,41 @@
       <c r="C22" s="3" t="n">
         <v>123.3</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
+      <c r="E22" s="11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H22" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K22" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>68.90000000000001</v>
+      <c r="L22" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1</v>
+        <v>91.8</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2325,20 +2340,20 @@
       <c r="Q22" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>740.8</v>
+        <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>12</v>
+      <c r="V22" s="11" t="n">
+        <v>17.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2347,10 +2362,10 @@
         <v>18.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2366,51 +2381,49 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>477.4</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="D23" s="11" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>91</v>
+      <c r="E23" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>91.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2654</v>
+        <v>94.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>636.4</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>80.8</v>
-      </c>
+        <v>61.2</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K23" s="11" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>161.4</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>14.6</v>
+      <c r="K23" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>12.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="11" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2422,17 +2435,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>919.8</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>83.90000000000001</v>
+      <c r="V23" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>942.1</v>
+        <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>148.8</v>
+        <v>929.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2453,20 +2466,20 @@
       <c r="C24" s="3" t="n">
         <v>215.4</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>636.4</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2475,28 +2488,28 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>43.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>221.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>47.8</v>
+      <c r="R24" s="11" t="n">
+        <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.1</v>
@@ -2507,14 +2520,14 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2536,76 +2549,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>130.4</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="13" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L25" s="11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>34.2</v>
+      <c r="L25" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>84.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>910.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q25" s="11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R25" s="13" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="S25" s="8" t="n">
-        <v>17.6</v>
+        <v>91.5</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="W25" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>94</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2621,16 +2632,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>23.5</v>
+        <v>32.6</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>22.5</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>18.9</v>
+        <v>13.6</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.9</v>
@@ -2639,19 +2650,19 @@
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>14.9</v>
+        <v>3.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>11.5</v>
@@ -2660,13 +2671,13 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q26" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>17.3</v>
+      <c r="R26" s="8" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2677,20 +2688,20 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="W26" s="11" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2706,49 +2717,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>14.1</v>
+        <v>12.8</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.6</v>
+        <v>18.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q27" s="11" t="n">
-        <v>20.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>17.9</v>
@@ -2757,16 +2766,16 @@
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>71</v>
+        <v>717</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V27" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W27" s="11" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
@@ -2791,40 +2800,40 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>21.9</v>
+        <v>30.5</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L28" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.4</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2832,14 +2841,14 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="11" t="n">
-        <v>20.5</v>
+      <c r="Q28" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.2</v>
+        <v>41.5</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>72.8</v>
@@ -2847,7 +2856,7 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="W28" s="11" t="n">
@@ -2860,7 +2869,7 @@
         <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2878,46 +2887,46 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="11" t="n">
         <v>21.9</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>84.5</v>
+        <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L29" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="13" t="n">
-        <v>84.40000000000001</v>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
@@ -2927,19 +2936,19 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W29" s="11" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>18.2</v>
+      <c r="X29" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2961,73 +2970,69 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1689.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>1609.9</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>1129.8</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="F30" s="9" t="n">
+      <c r="E30" s="14" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.7</v>
+        <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K30" s="10" t="n">
         <v>38.6</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L30" s="14" t="inlineStr"/>
+      <c r="M30" s="10" t="n">
         <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.6</v>
+        <v>7.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>479.8</v>
+        <v>0.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>27.4</v>
+      <c r="R30" s="10" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.8</v>
+        <v>561</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>394.6</v>
-      </c>
-      <c r="V30" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="9" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="W30" s="11" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.8</v>
+        <v>441</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>12.2</v>
@@ -3048,20 +3053,20 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E31" s="9" t="n">
+      <c r="D31" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>28.2</v>
+        <v>18.3</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3069,53 +3074,49 @@
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>1.4</v>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="10" t="n">
+        <v>14.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>116.3</v>
+        <v>29.3</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V31" s="11" t="n">
-        <v>17.6</v>
+        <v>6.9</v>
+      </c>
+      <c r="V31" s="10" t="n">
+        <v>18.6</v>
       </c>
       <c r="W31" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.7</v>
+        <v>1.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.3</v>
+        <v>119.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.4</v>
+        <v>214.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3131,40 +3132,38 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>481.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>71.90000000000001</v>
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M32" s="13" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M32" s="9" t="n">
         <v>10.51</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>16.1</v>
+      <c r="N32" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3175,14 +3174,14 @@
       <c r="Q32" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="8" t="n">
-        <v>15.8</v>
+      <c r="R32" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
@@ -3194,13 +3193,13 @@
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3216,46 +3215,46 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>422.8</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>6618.45</v>
+        <v>1482.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.9</v>
+        <v>86.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3267,7 +3266,7 @@
         <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>319.5</v>
+        <v>21.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
@@ -3275,11 +3274,11 @@
       <c r="V33" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>16.6</v>
+      <c r="W33" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>71</v>
@@ -3301,28 +3300,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>3.6</v>
+        <v>482.8</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G34" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G34" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>18.3</v>
+      <c r="H34" s="8" t="n">
+        <v>109.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3330,11 +3329,11 @@
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="13" t="n">
-        <v>91.59999999999999</v>
+      <c r="M34" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3345,8 +3344,8 @@
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="13" t="n">
-        <v>1.7</v>
+      <c r="R34" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3361,15 +3360,15 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="Z34" s="3" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3384,25 +3383,25 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>18</v>
+        <v>9492.799999999999</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>0.4</v>
+      <c r="F35" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>279.3</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.4</v>
+        <v>44.6</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
@@ -3414,19 +3413,19 @@
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.8</v>
+        <v>11.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>90</v>
+        <v>910</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>24.8</v>
+      <c r="Q35" s="9" t="n">
+        <v>94.5</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
@@ -3435,22 +3434,22 @@
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60</v>
+        <v>600.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="V35" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>18.5</v>
+      <c r="W35" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.5</v>
+        <v>125.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3469,25 +3468,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>498.3</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E36" s="3" t="n">
+        <v>9498.9</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="13" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>10.3</v>
+      <c r="F36" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>410.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3495,14 +3494,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>16.6</v>
+      <c r="L36" s="9" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>81.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3510,20 +3509,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>29.2</v>
+      <c r="Q36" s="9" t="n">
+        <v>88.09999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="V36" s="11" t="n">
         <v>18.4</v>
@@ -3531,14 +3530,14 @@
       <c r="W36" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="8" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3554,76 +3553,74 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>128.1</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>92.59999999999999</v>
+        <v>2192.8</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>18.8</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>711.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>44930.3</v>
+        <v>4420.3</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q37" s="10" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="10" t="n">
         <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>24.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>234.8</v>
       </c>
       <c r="V37" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="9" t="n">
-        <v>80.90000000000001</v>
+      <c r="W37" s="10" t="n">
+        <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>83.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>41252.4</v>
+        <v>409.8</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>4.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3639,58 +3636,56 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="D38" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="E38" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F38" s="9" t="n">
+      <c r="E38" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F38" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M38" s="9" t="n">
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="10" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="M38" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="8" t="n">
-        <v>58.1</v>
+      <c r="N38" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>89.8</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>480.5</v>
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>63.9</v>
+        <v>82.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3698,17 +3693,17 @@
       <c r="V38" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>15.1</v>
+      <c r="W38" s="10" t="n">
+        <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>4</v>
+        <v>89.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3724,76 +3719,72 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2392.3</v>
+        <v>39595.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>23</v>
+        <v>24.2</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>11.9</v>
+      <c r="G39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>19</v>
+      <c r="S39" s="8" t="n">
+        <v>20.9</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="13" t="n">
-        <v>1.9</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="V39" s="13" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="X39" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>71</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3809,42 +3800,46 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2942.1</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>49.2</v>
+        <v>545.4</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="12" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>23.8</v>
@@ -3853,7 +3848,7 @@
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>58.8</v>
@@ -3864,17 +3859,17 @@
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>12.1</v>
+      <c r="W40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.2</v>
+        <v>408.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3890,28 +3885,28 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>408.4</v>
-      </c>
-      <c r="D41" s="3" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D41" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>13.1</v>
+        <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H41" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>81</v>
+      <c r="I41" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3919,45 +3914,47 @@
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M41" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R41" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>17.8</v>
+      <c r="Q41" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>83</v>
+        <v>113.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3973,50 +3970,52 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>340.1</v>
+        <v>331</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
+        <v>11.4</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H42" s="3" t="n">
-        <v>13.7</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>1.3</v>
+        <v>16.2</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>14.6</v>
+        <v>16.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="R42" s="13" t="n">
-        <v>4.8</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
@@ -4028,17 +4027,19 @@
         <v>10.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>18.2</v>
+        <v>20.4</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>12.1</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>110.1</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>58</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4054,74 +4055,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>537</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="E43" s="12" t="inlineStr"/>
+        <v>557.1</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>1.2</v>
+      </c>
       <c r="F43" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>1.4</v>
+        <v>28.8</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="13" t="n">
-        <v>1.6</v>
+      <c r="R43" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W43" s="13" t="n">
-        <v>0.1</v>
+        <v>186.7</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>16.2</v>
+        <v>5</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4137,63 +4140,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>223.1</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>12.6</v>
+        <v>2983</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="H44" s="3" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2.6</v>
+        <v>15.2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5</v>
+        <v>26.2</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O44" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>340.9</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R44" s="13" t="n">
-        <v>67.09999999999999</v>
+        <v>10.6</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>13.9</v>
+        <v>97.5</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W44" s="12" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>351</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="V44" s="9" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="W44" s="9" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>28.1</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4208,76 +4225,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2282</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>1981.8</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>110.8</v>
+        <v>497</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>18.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>10.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.8</v>
+        <v>11.8</v>
       </c>
       <c r="I45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>286.2</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>31.3</v>
-      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
+        <v>10.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>922.8</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>17.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>92.2</v>
+        <v>16.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>331</v>
+        <v>58.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>22</v>
+        <v>11.5</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>15.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>36</v>
+        <v>16.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>966.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>44.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4295,70 +4312,74 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>18.4</v>
+      <c r="D46" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>0.1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.3</v>
+        <v>145.9</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>6.8</v>
+      <c r="M46" s="10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>20.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>17.1</v>
+      <c r="Q46" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R46" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>15.9</v>
+        <v>11.8</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>1414</v>
+      </c>
+      <c r="V46" s="10" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="W46" s="10" t="n">
+        <v>11151.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>16.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>77.8</v>
+        <v>112</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>4.8</v>
+        <v>15.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -53,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -159,9 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -789,7 +786,7 @@
       <c r="D4" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -813,11 +810,11 @@
       <c r="L4" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>29.5</v>
+      <c r="N4" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -825,7 +822,7 @@
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="3" t="n">
         <v>25</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -835,13 +832,13 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>18.7</v>
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -861,12 +858,12 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="E5" s="11" t="n">
+        <v>388.3</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="F5" s="3" t="n">
@@ -875,62 +872,62 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.8</v>
+      <c r="H5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L5" s="9" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q5" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W5" s="11" t="n">
-        <v>17.6</v>
+        <v>13</v>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
+        <v>13.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -946,48 +943,48 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>50.8</v>
+        <v>508.9</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>12.8</v>
+      <c r="E6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18.5</v>
+        <v>13.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.1</v>
+        <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -997,25 +994,25 @@
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.5</v>
+        <v>18.5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>10.4</v>
+        <v>512.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>16.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27</v>
+        <v>17.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1031,76 +1028,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
+        <v>22.9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
+        <v>21.5</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>98</v>
+        <v>29.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15.8</v>
+        <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>52.4</v>
+        <v>22.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R7" s="9" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>17.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.1</v>
+        <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>16.6</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.5</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1116,76 +1113,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>17.7</v>
+        <v>22.2</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.7</v>
+        <v>50.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>63.1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.9</v>
+        <v>706.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.8</v>
+        <v>260.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>14.1</v>
+        <v>51.1</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>60.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>40.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.6</v>
+        <v>59</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>11.4</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1201,75 +1198,77 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>222.4</v>
+        <v>445</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1118.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>67.59999999999999</v>
+        <v>23.7</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>13.5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>93.09999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>30.9</v>
+        <v>10.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.1</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>706.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>260.4</v>
+        <v>3.3</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>51.1</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>73.40000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>0.2</v>
+        <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59</v>
+        <v>21.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>114</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>22.8</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>88.09999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.2</v>
+        <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>212.6</v>
+        <v>21.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>23</v>
+        <v>1.1</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>115.1</v>
+        <v>94</v>
       </c>
       <c r="W9" s="10" t="n">
         <v>16</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>117.8</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1284,12 +1283,12 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>13.5</v>
       </c>
       <c r="F10" s="10" t="n">
@@ -1299,32 +1298,34 @@
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J10" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M10" s="10" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="N10" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>15.8</v>
-      </c>
       <c r="O10" s="3" t="n">
-        <v>99.8</v>
+        <v>15.3</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="Q10" s="10" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q10" s="11" t="n">
-        <v>22.8</v>
       </c>
       <c r="R10" s="10" t="n">
         <v>17.6</v>
@@ -1333,7 +1334,7 @@
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1341,17 +1342,17 @@
       <c r="V10" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>83</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,8 +1370,8 @@
       <c r="C11" s="3" t="n">
         <v>191.8</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>22</v>
+      <c r="D11" s="12" t="n">
+        <v>22.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>13.7</v>
@@ -1379,7 +1380,7 @@
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
@@ -1391,53 +1392,43 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.9</v>
+        <v>17.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q11" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="R11" s="9" t="n">
-        <v>1.1</v>
+      <c r="Q11" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>17.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>140649.1</v>
+        <v>212.4</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="W11" s="9" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>717.5</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>80494</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
+      <c r="W11" s="11" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1454,11 +1445,11 @@
       <c r="C12" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="12" t="n">
         <v>22.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17.9</v>
@@ -1466,7 +1457,7 @@
       <c r="G12" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1478,40 +1469,40 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M12" s="9" t="n">
-        <v>83.90000000000001</v>
+      <c r="M12" s="12" t="n">
+        <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R12" s="3" t="n">
+      <c r="Q12" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R12" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>24.8</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="W12" s="13" t="inlineStr"/>
+      <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1535,7 +1526,7 @@
       <c r="C13" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="12" t="n">
         <v>23.6</v>
       </c>
       <c r="E13" s="3" t="n">
@@ -1548,7 +1539,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1562,35 +1553,35 @@
       <c r="L13" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="12" t="n">
         <v>15.8</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.9</v>
+        <v>74.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>14.8</v>
@@ -1618,9 +1609,9 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="E14" s="3" t="n">
@@ -1636,58 +1627,58 @@
         <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>56.8</v>
+        <v>26.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W14" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1705,8 +1696,8 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>24.8</v>
+      <c r="D15" s="12" t="n">
+        <v>24.5</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>13.2</v>
@@ -1718,36 +1709,36 @@
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>25</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1757,7 +1748,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1791,28 +1782,28 @@
         <v>147.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>114.8</v>
+        <v>14.8</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>674.7</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>164.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="L16" s="10" t="n">
         <v>73.2</v>
@@ -1821,19 +1812,19 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1140.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>83</v>
+      <c r="R16" s="12" t="n">
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1842,7 +1833,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16" s="10" t="n">
         <v>84.3</v>
@@ -1851,10 +1842,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1208.8</v>
+        <v>158.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1873,16 +1864,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>295</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>18</v>
+        <v>29.5</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>23</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1894,30 +1885,30 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>69.5</v>
+        <v>121.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="L17" s="10" t="n">
         <v>14.6</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <v>19.1</v>
+      <c r="M17" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="12" t="n">
         <v>19.3</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1927,7 +1918,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="V17" s="10" t="n">
         <v>5</v>
@@ -1939,7 +1930,7 @@
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>15.3</v>
@@ -1958,25 +1949,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.3</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="E18" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>48.4</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1984,10 +1975,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -2000,7 +1991,7 @@
       <c r="Q18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2010,16 +2001,16 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V18" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="X18" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>84</v>
@@ -2041,18 +2032,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>440.6</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2067,25 +2058,25 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="9" t="n">
-        <v>1.4</v>
+      <c r="M19" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R19" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R19" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2097,11 +2088,11 @@
       <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W19" s="9" t="n">
-        <v>87</v>
+      <c r="V19" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W19" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>18.3</v>
@@ -2110,7 +2101,7 @@
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>17.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2128,49 +2119,49 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.8</v>
+        <v>8.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2182,10 +2173,10 @@
       <c r="U20" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2211,51 +2202,51 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>261.7</v>
-      </c>
-      <c r="D21" s="11" t="n">
+        <v>251.7</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>11.7</v>
+        <v>1.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99.8</v>
+        <v>90.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R21" s="11" t="n">
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R21" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2267,10 +2258,10 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2296,43 +2287,43 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="11" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>1.4</v>
+      <c r="L22" s="12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2340,7 +2331,7 @@
       <c r="Q22" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2352,10 +2343,10 @@
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2365,7 +2356,7 @@
         <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2383,33 +2374,33 @@
       <c r="C23" s="3" t="n">
         <v>177.2</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>29.4</v>
+      <c r="E23" s="12" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>91.8</v>
+        <v>92.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>94.3</v>
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>61.2</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>16.2</v>
+      <c r="L23" s="12" t="n">
+        <v>76.2</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>30.4</v>
@@ -2423,11 +2414,11 @@
       <c r="Q23" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="12" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2435,8 +2426,8 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="11" t="n">
-        <v>91.90000000000001</v>
+      <c r="V23" s="10" t="n">
+        <v>91.3</v>
       </c>
       <c r="W23" s="10" t="n">
         <v>81.09999999999999</v>
@@ -2445,7 +2436,7 @@
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>929.5</v>
+        <v>35.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2464,22 +2455,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>12.9</v>
+        <v>22.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2488,19 +2479,19 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>43.4</v>
+        <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>221.1</v>
+        <v>22.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2508,7 +2499,7 @@
       <c r="Q24" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2520,10 +2511,10 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="11" t="n">
+      <c r="V24" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2549,16 +2540,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>22.6</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>18.8</v>
+        <v>13</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9</v>
@@ -2576,10 +2567,10 @@
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>84.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1.5</v>
@@ -2588,14 +2579,14 @@
         <v>91.5</v>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
+      <c r="Q25" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R25" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2603,10 +2594,10 @@
       <c r="U25" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2632,9 +2623,9 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>326</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>22.5</v>
       </c>
       <c r="E26" s="3" t="n">
@@ -2647,7 +2638,7 @@
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2658,14 +2649,14 @@
       <c r="K26" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>1.4</v>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2673,11 +2664,11 @@
       <c r="P26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="R26" s="12" t="n">
+        <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2688,20 +2679,20 @@
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="12" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2717,12 +2708,12 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="F27" s="9" t="n">
@@ -2732,7 +2723,7 @@
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
@@ -2741,14 +2732,14 @@
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2756,25 +2747,25 @@
       <c r="P27" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R27" s="3" t="n">
+      <c r="Q27" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>717</v>
+        <v>77</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2800,9 +2791,9 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="E28" s="3" t="n">
@@ -2815,7 +2806,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>82.8</v>
+        <v>23.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2823,17 +2814,17 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2841,10 +2832,10 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2856,20 +2847,20 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2887,14 +2878,14 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="12" t="n">
         <v>21.9</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>17.5</v>
+      <c r="F29" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.1</v>
@@ -2903,22 +2894,22 @@
         <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2926,29 +2917,29 @@
       <c r="P29" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q29" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R29" s="3" t="n">
+      <c r="Q29" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R29" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="11" t="n">
+      <c r="W29" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>82.09999999999999</v>
+      <c r="X29" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2973,9 +2964,9 @@
         <v>1609.9</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1129.8</v>
-      </c>
-      <c r="E30" s="14" t="inlineStr"/>
+        <v>112.9</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="10" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -2983,23 +2974,23 @@
         <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L30" s="14" t="inlineStr"/>
-      <c r="M30" s="10" t="n">
-        <v>11.7</v>
+        <v>35.6</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="12" t="n">
+        <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.9</v>
+        <v>79.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3007,29 +2998,29 @@
       <c r="P30" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="12" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="12" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561</v>
+        <v>361.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="V30" s="10" t="n">
         <v>88.8</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>441</v>
@@ -3053,7 +3044,7 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>22.5</v>
       </c>
       <c r="E31" s="3" t="n">
@@ -3076,11 +3067,11 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="10" t="n">
-        <v>14.7</v>
+      <c r="M31" s="12" t="n">
+        <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16.8</v>
@@ -3088,35 +3079,35 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>29.3</v>
+        <v>79.8</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V31" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+      <c r="V31" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>119.2</v>
+        <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>214.4</v>
+        <v>24.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3132,9 +3123,9 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D32" s="13" t="inlineStr"/>
+        <v>235.5</v>
+      </c>
+      <c r="D32" s="11" t="inlineStr"/>
       <c r="E32" s="3" t="n">
         <v>14.2</v>
       </c>
@@ -3142,7 +3133,7 @@
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3156,14 +3147,14 @@
       <c r="K32" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>16.8</v>
+      <c r="L32" s="12" t="n">
+        <v>16.3</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.51</v>
       </c>
-      <c r="N32" s="8" t="n">
-        <v>12.8</v>
+      <c r="N32" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3171,14 +3162,14 @@
       <c r="P32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>18.8</v>
+      <c r="R32" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
@@ -3186,20 +3177,20 @@
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="V32" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3215,22 +3206,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>82.59999999999999</v>
+      <c r="H33" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3239,49 +3230,49 @@
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>84.8</v>
+      <c r="N33" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>21.2</v>
+        <v>51.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="V33" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="12" t="n">
         <v>15.4</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3302,8 +3293,8 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>44.1</v>
+      <c r="D34" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>11.5</v>
@@ -3311,14 +3302,14 @@
       <c r="F34" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>109.5</v>
+      <c r="H34" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.9</v>
@@ -3326,14 +3317,14 @@
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="12" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+      <c r="M34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3341,11 +3332,11 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>17.8</v>
+      <c r="R34" s="12" t="n">
+        <v>17.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3356,17 +3347,17 @@
       <c r="U34" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V34" s="11" t="n">
+      <c r="V34" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W34" s="3" t="n">
-        <v>12.8</v>
+      <c r="W34" s="12" t="n">
+        <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3383,19 +3374,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>9492.799999999999</v>
+        <v>492.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="9" t="n">
-        <v>1.9</v>
+      <c r="F35" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>279.3</v>
@@ -3409,47 +3400,47 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>910</v>
+        <v>10</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="9" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
+      <c r="Q35" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R35" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V35" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V35" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>82.8</v>
+      <c r="W35" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>125.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3468,19 +3459,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9498.9</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E36" s="8" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>410.3</v>
+        <v>12.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
@@ -3494,14 +3485,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>86.59999999999999</v>
+      <c r="L36" s="12" t="n">
+        <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>17.4</v>
+      <c r="N36" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3509,35 +3500,35 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="9" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R36" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V36" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V36" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>66.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3553,7 +3544,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2192.8</v>
+        <v>192.8</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>119.1</v>
@@ -3569,55 +3560,53 @@
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
-        <v>110.6</v>
+        <v>10.6</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L37" s="10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>75.7</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>711.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>4420.3</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="12" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>81</v>
+      <c r="R37" s="12" t="n">
+        <v>87</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>313.4</v>
+        <v>13.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
-      </c>
-      <c r="V37" s="11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="V37" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="12" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.8</v>
+        <v>9.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3636,7 +3625,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.8</v>
+        <v>438.6</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>23.8</v>
@@ -3651,10 +3640,10 @@
         <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
@@ -3667,33 +3656,33 @@
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>82.7</v>
+        <v>62.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="12" t="n">
         <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3719,15 +3708,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>39595.3</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>24.2</v>
+        <v>595.3</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>24.5</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3736,18 +3725,16 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
+      <c r="M39" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3758,14 +3745,14 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>20.9</v>
+      <c r="S39" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
@@ -3773,11 +3760,11 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="13" t="inlineStr"/>
+      <c r="V39" s="12" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3802,13 +3789,13 @@
       <c r="C40" s="3" t="n">
         <v>545.4</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>29.3</v>
+      <c r="D40" s="12" t="n">
+        <v>24.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F40" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3823,17 +3810,17 @@
       <c r="J40" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>0.8</v>
+      <c r="K40" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>19</v>
+      <c r="M40" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3841,35 +3828,35 @@
       <c r="P40" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="3" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>408.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3885,37 +3872,37 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="8" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>23.7</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F41" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>19.2</v>
@@ -3926,35 +3913,35 @@
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="T41" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="X41" s="3" t="n">
-        <v>14.6</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>113.8</v>
+        <v>82</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3970,22 +3957,22 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F42" s="3" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>18.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
@@ -3993,28 +3980,28 @@
       <c r="J42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>0.9</v>
+      <c r="K42" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>15.1</v>
+        <v>13.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.1</v>
+        <v>19.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4026,20 +4013,20 @@
       <c r="U42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>20.4</v>
+      <c r="V42" s="12" t="n">
+        <v>18.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>18.1</v>
+        <v>22.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>110.1</v>
+        <v>28</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>58</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4055,76 +4042,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>557.1</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>18</v>
+        <v>537</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>18.1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>99.59999999999999</v>
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>35.4</v>
+        <v>16.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V43" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>22.6</v>
+        <v>58</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>557.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4140,76 +4127,74 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2983</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>10.5</v>
+        <v>22.1</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>18</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>62</v>
+        <v>10.8</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L44" s="9" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R44" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="V44" s="9" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="W44" s="9" t="n">
-        <v>95.5</v>
+      <c r="V44" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>466.8</v>
+        <v>13.6</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>28.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4225,76 +4210,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>497</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>23.6</v>
+        <v>2983</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>141.7</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>13.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>18.4</v>
+        <v>10.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.3</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.8</v>
+        <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K45" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="L45" s="10" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="M45" s="10" t="n">
-        <v>0.6</v>
+        <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>10.1</v>
+        <v>540.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>922.8</v>
-      </c>
-      <c r="R45" s="10" t="n">
-        <v>17.1</v>
+        <v>12.7</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>102.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>97.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>58.5</v>
+        <v>351</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.5</v>
+        <v>69</v>
       </c>
       <c r="V45" s="10" t="n">
-        <v>118.6</v>
+        <v>111.5</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>15.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>16.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>82.8</v>
+        <v>468.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>44.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4312,38 +4297,38 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>0.1</v>
+      <c r="D46" s="12" t="n">
+        <v>23.6</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>0.1</v>
+        <v>13.3</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>145.9</v>
+        <v>19.3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>12</v>
+        <v>20.4</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>90.09999999999999</v>
@@ -4351,35 +4336,35 @@
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R46" s="10" t="n">
-        <v>1.8</v>
+      <c r="Q46" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.8</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1414</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>117.5</v>
+        <v>11.5</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="W46" s="10" t="n">
-        <v>11151.1</v>
+        <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.8</v>
+        <v>55.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.1</v>
+        <v>11.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>58.5</v>
+        <v>585.3</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>25.1</v>
@@ -817,7 +817,7 @@
         <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2.2</v>
@@ -861,7 +861,7 @@
         <v>388.3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
@@ -870,7 +870,7 @@
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>12.3</v>
@@ -979,7 +979,7 @@
         <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -991,7 +991,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22.9</v>
+        <v>229.6</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>21.5</v>
@@ -1046,25 +1046,25 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29.9</v>
+        <v>27.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1094,7 +1094,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>22.2</v>
+        <v>2224.9</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>11.85</v>
@@ -1143,10 +1143,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1164,7 +1164,7 @@
         <v>86.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>12.6</v>
+        <v>312.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>53</v>
@@ -1216,7 +1216,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>229.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1231,7 +1231,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1249,10 +1249,10 @@
         <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="V9" s="10" t="n">
         <v>94</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>45</v>
+        <v>145.5</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>23.7</v>
@@ -1310,7 +1310,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>14.7</v>
@@ -1334,7 +1334,7 @@
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1392,16 +1392,16 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>15.3</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1419,7 +1419,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>212.4</v>
+        <v>22.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1469,17 +1469,17 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="12" t="n">
         <v>14.3</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W12" s="11" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1550,7 +1550,7 @@
       <c r="K13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M13" s="12" t="n">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
+        <v>324</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>21.8</v>
@@ -1635,7 +1635,7 @@
       <c r="K14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="M14" s="12" t="n">
@@ -1678,7 +1678,7 @@
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
       <c r="K15" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="M15" s="12" t="n">
@@ -1730,7 +1730,7 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1748,7 +1748,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>14.8</v>
+        <v>1475.2</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>114.8</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>674.7</v>
@@ -1803,19 +1803,19 @@
         <v>6.9</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="L16" s="10" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>73.2</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>12.4</v>
+        <v>712.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
@@ -1823,8 +1823,8 @@
       <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="12" t="n">
-        <v>83.5</v>
+      <c r="R16" s="10" t="n">
+        <v>83.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1833,7 +1833,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="V16" s="10" t="n">
         <v>84.3</v>
@@ -1845,7 +1845,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>158.8</v>
+        <v>450.2</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>23</v>
+        <v>295</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>28</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>12.5</v>
+        <v>18.6</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1885,22 +1885,22 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>121.4</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="L17" s="10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <v>14.6</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.2</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1975,7 +1975,7 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2001,7 +2001,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>18.5</v>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>40.6</v>
+        <v>440.6</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>25</v>
@@ -2044,7 +2044,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2058,7 +2058,7 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2071,7 +2071,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2120,7 +2120,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>13.8</v>
@@ -2129,7 +2129,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.9</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2138,19 +2138,19 @@
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>17.8</v>
+        <v>14.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2171,7 +2171,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>17.6</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>251.7</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>21.9</v>
@@ -2228,14 +2228,14 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2313,14 +2313,14 @@
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>15.5</v>
+      <c r="L22" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.1</v>
+        <v>16.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2374,20 +2374,20 @@
       <c r="C23" s="3" t="n">
         <v>177.2</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="10" t="n">
         <v>113.1</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>92.5</v>
+      <c r="F23" s="12" t="n">
+        <v>91.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
@@ -2396,7 +2396,7 @@
       <c r="K23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="L23" s="10" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="10" t="n">
@@ -2418,7 +2418,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.5</v>
+        <v>90.3</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2427,7 +2427,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>91.3</v>
+        <v>22.8</v>
       </c>
       <c r="W23" s="10" t="n">
         <v>81.09999999999999</v>
@@ -2436,7 +2436,7 @@
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>35.5</v>
+        <v>435.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>29.5</v>
+        <v>295.4</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>22.6</v>
@@ -2470,7 +2470,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2479,19 +2479,19 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L24" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="10" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>22.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2563,7 +2563,7 @@
       <c r="J25" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="12" t="n">
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2573,7 +2573,7 @@
         <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.5</v>
+        <v>15.7</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>91.5</v>
@@ -2646,8 +2646,8 @@
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.9</v>
+      <c r="K26" s="12" t="n">
+        <v>3.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>14.6</v>
@@ -2656,7 +2656,7 @@
         <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2668,7 +2668,7 @@
         <v>20.7</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>288.8</v>
+        <v>287.8</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>23.5</v>
@@ -2729,7 +2729,7 @@
       <c r="J27" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="L27" s="3" t="n">
@@ -2800,13 +2800,13 @@
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2814,7 +2814,7 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2891,7 +2891,7 @@
         <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13.8</v>
+        <v>33.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.3</v>
@@ -2899,8 +2899,8 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>1.8</v>
+      <c r="K29" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>14.9</v>
@@ -2909,7 +2909,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.1</v>
+        <v>21.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2918,7 +2918,7 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="R29" s="12" t="n">
         <v>17.8</v>
@@ -2982,7 +2982,7 @@
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="12" t="n">
         <v>35.6</v>
       </c>
       <c r="L30" s="13" t="inlineStr"/>
@@ -2990,7 +2990,7 @@
         <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -3008,13 +3008,13 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.9</v>
+        <v>361.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
       </c>
-      <c r="V30" s="10" t="n">
-        <v>88.8</v>
+      <c r="V30" s="12" t="n">
+        <v>87.8</v>
       </c>
       <c r="W30" s="12" t="n">
         <v>81.09999999999999</v>
@@ -3071,10 +3071,10 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
@@ -3086,10 +3086,10 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>18.1</v>
+        <v>181.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.8</v>
+        <v>72.3</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
@@ -3107,7 +3107,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>24.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
         <v>235.5</v>
       </c>
       <c r="D32" s="11" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3144,7 +3144,7 @@
       <c r="J32" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="L32" s="12" t="n">
@@ -3154,7 +3154,7 @@
         <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3169,13 +3169,13 @@
         <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>15.9</v>
@@ -3190,7 +3190,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3206,22 +3206,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
+        <v>1482.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="12" t="n">
         <v>18.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3229,8 +3229,8 @@
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>1.8</v>
+      <c r="K33" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>13.7</v>
@@ -3239,7 +3239,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3296,17 +3296,17 @@
       <c r="D34" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="12" t="n">
         <v>11.5</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.3</v>
@@ -3314,7 +3314,7 @@
       <c r="J34" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
@@ -3354,7 +3354,7 @@
         <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>81</v>
@@ -3379,10 +3379,10 @@
       <c r="D35" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="12" t="n">
         <v>19.3</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3397,7 +3397,7 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
@@ -3407,10 +3407,10 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
@@ -3459,16 +3459,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>498.9</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
+      <c r="F36" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.3</v>
@@ -3482,7 +3482,7 @@
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
@@ -3492,7 +3492,7 @@
         <v>15.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3525,10 +3525,10 @@
         <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>192.8</v>
+        <v>2192.8</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>119.1</v>
@@ -3565,7 +3565,7 @@
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="L37" s="12" t="n">
@@ -3591,7 +3591,7 @@
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.8</v>
@@ -3603,10 +3603,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>9.5</v>
+        <v>409.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3630,17 +3630,17 @@
       <c r="D38" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="E38" s="10" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F38" s="10" t="n">
+      <c r="E38" s="12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.1</v>
@@ -3656,10 +3656,10 @@
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
@@ -3713,7 +3713,7 @@
       <c r="D39" s="12" t="n">
         <v>24.5</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="12" t="n">
         <v>13</v>
       </c>
       <c r="F39" s="12" t="n">
@@ -3725,16 +3725,18 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>1.5</v>
+        <v>28.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3760,8 +3762,8 @@
       <c r="U39" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="V39" s="12" t="inlineStr"/>
-      <c r="W39" s="3" t="n">
+      <c r="V39" s="11" t="inlineStr"/>
+      <c r="W39" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3790,16 +3792,16 @@
         <v>545.4</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E40" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E40" s="12" t="n">
         <v>13.8</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3820,7 +3822,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3843,14 +3845,14 @@
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="12" t="n">
+      <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="12" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>82</v>
@@ -3877,8 +3879,8 @@
       <c r="D41" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>12.5</v>
+      <c r="E41" s="12" t="n">
+        <v>12.2</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>18.1</v>
@@ -3926,13 +3928,13 @@
         <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V41" s="12" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>18</v>
+      <c r="W41" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3962,8 +3964,8 @@
       <c r="D42" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="E42" s="9" t="n">
-        <v>1.4</v>
+      <c r="E42" s="12" t="n">
+        <v>14.1</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>18.5</v>
@@ -3987,7 +3989,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.2</v>
+        <v>22.6</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -4013,17 +4015,17 @@
       <c r="U42" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4047,7 +4049,7 @@
       <c r="D43" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="12" t="n">
         <v>13.1</v>
       </c>
       <c r="F43" s="12" t="n">
@@ -4075,7 +4077,7 @@
         <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
@@ -4098,11 +4100,11 @@
       <c r="U43" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V43" s="12" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>15.8</v>
+      <c r="V43" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W43" s="12" t="n">
+        <v>15.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>4.2</v>
@@ -4127,12 +4129,12 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22.1</v>
+        <v>237.1</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>23.4</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="12" t="n">
         <v>12.6</v>
       </c>
       <c r="F44" s="12" t="n">
@@ -4160,7 +4162,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4173,7 +4175,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4181,10 +4183,10 @@
       <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="V44" s="12" t="n">
+      <c r="V44" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
@@ -4216,7 +4218,7 @@
         <v>141.7</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>97.09999999999999</v>
+        <v>797.1</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>10.5</v>
@@ -4243,7 +4245,7 @@
         <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>540.9</v>
@@ -4252,7 +4254,7 @@
         <v>10.6</v>
       </c>
       <c r="Q45" s="10" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="R45" s="12" t="n">
         <v>102.4</v>
@@ -4270,13 +4272,13 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>95.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>468.8</v>
+        <v>466.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>28.7</v>
@@ -4300,14 +4302,14 @@
       <c r="D46" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.3</v>
+        <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>11.8</v>
@@ -4319,13 +4321,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="10" t="n">
-        <v>20.4</v>
+        <v>8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4351,17 +4353,17 @@
       <c r="U46" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="12" t="n">
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>55.4</v>
+        <v>11.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>11.4</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>585.3</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>25.1</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.3</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>23.9</v>
@@ -885,13 +885,13 @@
         <v>15.7</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
@@ -976,10 +976,10 @@
         <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -991,7 +991,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17.3</v>
+        <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1046,7 +1046,7 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
@@ -1064,7 +1064,7 @@
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1094,7 +1094,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2224.9</v>
+        <v>222.9</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>11.85</v>
@@ -1143,10 +1143,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>60.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1216,7 +1216,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>229.5</v>
+        <v>22.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1231,7 +1231,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1252,7 +1252,7 @@
         <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="V9" s="10" t="n">
         <v>94</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>23.7</v>
@@ -1298,10 +1298,10 @@
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>21.3</v>
@@ -1310,7 +1310,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>14.7</v>
@@ -1373,10 +1373,10 @@
       <c r="D11" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1392,7 +1392,7 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>15.3</v>
@@ -1401,7 +1401,7 @@
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1419,7 +1419,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22.6</v>
+        <v>2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1448,10 +1448,10 @@
       <c r="D12" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="12" t="n">
         <v>13.3</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1476,7 +1476,7 @@
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92</v>
@@ -1529,10 +1529,10 @@
       <c r="D13" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1614,10 +1614,10 @@
       <c r="D14" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1645,7 +1645,7 @@
         <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
@@ -1699,10 +1699,10 @@
       <c r="D15" s="12" t="n">
         <v>24.5</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1475.2</v>
+        <v>147.5</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>114.8</v>
@@ -1787,8 +1787,8 @@
       <c r="E16" s="10" t="n">
         <v>674.7</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>92.2</v>
+      <c r="F16" s="12" t="n">
+        <v>91.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>47.4</v>
@@ -1812,7 +1812,7 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>712.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>14.5</v>
@@ -1823,8 +1823,8 @@
       <c r="Q16" s="12" t="n">
         <v>96.5</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>83.2</v>
+      <c r="R16" s="12" t="n">
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1833,7 +1833,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16" s="10" t="n">
         <v>84.3</v>
@@ -1845,7 +1845,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>450.2</v>
+        <v>450</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1866,11 +1866,11 @@
       <c r="C17" s="3" t="n">
         <v>295</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>18.6</v>
+      <c r="D17" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>13.6</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>18.9</v>
@@ -1888,7 +1888,7 @@
         <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>14.6</v>
@@ -1897,10 +1897,10 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1975,7 +1975,7 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2001,7 +2001,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V18" s="12" t="n">
         <v>18.5</v>
@@ -2044,7 +2044,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2058,7 +2058,7 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="12" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2071,7 +2071,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2120,7 +2120,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>13.8</v>
@@ -2129,7 +2129,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2143,14 +2143,14 @@
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>14.8</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2171,7 +2171,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="V20" s="12" t="n">
         <v>17.6</v>
@@ -2228,14 +2228,14 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2313,14 +2313,14 @@
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>22</v>
+      <c r="L22" s="12" t="n">
+        <v>15.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2374,29 +2374,29 @@
       <c r="C23" s="3" t="n">
         <v>177.2</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="12" t="n">
         <v>113.1</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.3</v>
+        <v>64.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="12" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="10" t="n">
@@ -2427,7 +2427,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>22.8</v>
+        <v>91.3</v>
       </c>
       <c r="W23" s="10" t="n">
         <v>81.09999999999999</v>
@@ -2481,17 +2481,17 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="L24" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>400.4</v>
+        <v>40</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>22.6</v>
@@ -2739,7 +2739,7 @@
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2800,13 +2800,13 @@
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>13.8</v>
+        <v>83.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2857,7 +2857,7 @@
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>3.2</v>
@@ -2909,7 +2909,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.2</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2963,8 +2963,8 @@
       <c r="C30" s="3" t="n">
         <v>1609.9</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>112.9</v>
+      <c r="D30" s="12" t="n">
+        <v>112.5</v>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
       <c r="F30" s="10" t="n">
@@ -3008,7 +3008,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.2</v>
+        <v>36.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
@@ -3071,7 +3071,7 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16</v>
@@ -3086,7 +3086,7 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>181.1</v>
+        <v>181.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>72.3</v>
@@ -3107,7 +3107,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
       <c r="E32" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3154,7 +3154,7 @@
         <v>10.51</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3175,7 +3175,7 @@
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="V32" s="12" t="n">
         <v>15.9</v>
@@ -3190,7 +3190,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>24.2</v>
@@ -3214,14 +3214,14 @@
       <c r="E33" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>26.6</v>
+        <v>28.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3239,7 +3239,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3299,7 +3299,7 @@
       <c r="E34" s="12" t="n">
         <v>11.5</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3324,7 +3324,7 @@
         <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3382,8 +3382,8 @@
       <c r="E35" s="12" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="12" t="n">
-        <v>19.3</v>
+      <c r="F35" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>11.4</v>
@@ -3407,7 +3407,7 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>90</v>
@@ -3422,7 +3422,7 @@
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3467,7 +3467,7 @@
       <c r="E36" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3528,7 +3528,7 @@
         <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.2</v>
+        <v>409</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3633,11 +3633,11 @@
       <c r="E38" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>12.3</v>
@@ -3725,21 +3725,19 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>11.5</v>
+        <v>16</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1.6</v>
+        <v>30.1</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>94</v>
@@ -3801,7 +3799,7 @@
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>22.6</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3822,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3852,10 +3850,10 @@
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>6.2</v>
@@ -3880,7 +3878,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>18.1</v>
@@ -3907,7 +3905,7 @@
         <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3934,7 +3932,7 @@
         <v>19</v>
       </c>
       <c r="W41" s="12" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3989,7 +3987,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>22.6</v>
+        <v>13.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -4025,7 +4023,7 @@
         <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4129,7 +4127,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>237.1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="12" t="n">
         <v>23.4</v>
@@ -4162,7 +4160,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4175,7 +4173,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4212,7 +4210,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2983</v>
+        <v>298</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>141.7</v>
@@ -4272,7 +4270,7 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>22.2</v>
+        <v>95.5</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
@@ -4321,13 +4319,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4360,13 +4358,13 @@
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -1216,7 +1216,7 @@
       <c r="J9" s="3" t="n">
         <v>264.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>51.1</v>
       </c>
       <c r="L9" s="3" t="n"/>
@@ -1552,7 +1552,7 @@
       <c r="J13" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="K13" s="3" t="n"/>
+      <c r="K13" s="13" t="n"/>
       <c r="L13" s="3" t="n">
         <v>15</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="13" t="n"/>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
       </c>
@@ -1799,7 +1799,7 @@
       <c r="J16" s="3" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2368,7 +2368,7 @@
       <c r="J23" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>3321.1</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2947,7 +2947,7 @@
         <v>11565.6</v>
       </c>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>350.1</v>
       </c>
       <c r="L30" s="3" t="n"/>
@@ -3526,7 +3526,7 @@
       <c r="J37" s="3" t="n">
         <v>48.5</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>121.8</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4203,7 +4203,7 @@
       <c r="J45" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="L45" s="3" t="n">
